--- a/pdfs/checklist-veiculos-leves.xlsx
+++ b/pdfs/checklist-veiculos-leves.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/6a1be6d7d730111a/Desktop/check/check/pdfs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="905" documentId="8_{219FE2C1-C346-4449-8D1A-03A68A1BAB44}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9C46011C-8813-4C7B-BA79-55B722BE35B5}"/>
+  <xr:revisionPtr revIDLastSave="2" documentId="14_{E66D62EA-9596-4B51-B15F-8FC37881386A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5DBFAC29-BB0B-4701-B36A-FCA01D242D1C}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="910" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -342,7 +342,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="13" x14ac:knownFonts="1">
+  <fonts count="15" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -434,6 +434,23 @@
       <b/>
       <sz val="16"/>
       <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <u/>
+      <sz val="20"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="14"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -629,7 +646,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="144">
+  <cellXfs count="145">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -676,12 +693,6 @@
     <xf numFmtId="0" fontId="7" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -691,17 +702,297 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="8" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="8" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="8" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="8" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="8" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="8" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -721,45 +1012,12 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="12" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -769,9 +1027,6 @@
     <xf numFmtId="0" fontId="12" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -784,273 +1039,54 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="8" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="8" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="8" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="8" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="8" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="8" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="2">
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <color theme="6" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -1141,7 +1177,7 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="6130739" y="4078942"/>
+          <a:off x="6119533" y="4074868"/>
           <a:ext cx="346262" cy="245968"/>
           <a:chOff x="5939119" y="5076266"/>
           <a:chExt cx="334745" cy="291352"/>
@@ -1293,7 +1329,7 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="9400054" y="5921188"/>
+          <a:off x="9395980" y="5943600"/>
           <a:ext cx="257175" cy="228600"/>
           <a:chOff x="5939119" y="5076266"/>
           <a:chExt cx="334745" cy="291352"/>
@@ -1445,7 +1481,7 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="9400054" y="6212541"/>
+          <a:off x="9395980" y="6238009"/>
           <a:ext cx="257175" cy="228600"/>
           <a:chOff x="5939119" y="5076266"/>
           <a:chExt cx="334745" cy="291352"/>
@@ -1597,7 +1633,7 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="9400054" y="7603751"/>
+          <a:off x="9395980" y="7648575"/>
           <a:ext cx="257175" cy="228600"/>
           <a:chOff x="5939119" y="5076266"/>
           <a:chExt cx="334745" cy="291352"/>
@@ -1749,7 +1785,7 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="9409579" y="8186457"/>
+          <a:off x="9405505" y="8237393"/>
           <a:ext cx="257175" cy="228600"/>
           <a:chOff x="5939119" y="5076266"/>
           <a:chExt cx="334745" cy="291352"/>
@@ -1901,7 +1937,7 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="9400054" y="5328957"/>
+          <a:off x="9395980" y="5345257"/>
           <a:ext cx="257175" cy="228600"/>
           <a:chOff x="5939119" y="5076266"/>
           <a:chExt cx="334745" cy="291352"/>
@@ -2053,7 +2089,7 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="9412941" y="6488205"/>
+          <a:off x="9408867" y="6516729"/>
           <a:ext cx="257175" cy="228600"/>
           <a:chOff x="5939119" y="5076266"/>
           <a:chExt cx="334745" cy="291352"/>
@@ -2205,7 +2241,7 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="9419104" y="7885579"/>
+          <a:off x="9415030" y="7933459"/>
           <a:ext cx="257175" cy="228600"/>
           <a:chOff x="5939119" y="5076266"/>
           <a:chExt cx="334745" cy="291352"/>
@@ -2357,7 +2393,7 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="9412940" y="6790764"/>
+          <a:off x="9408866" y="6822344"/>
           <a:ext cx="257175" cy="228600"/>
           <a:chOff x="5939119" y="5076266"/>
           <a:chExt cx="334745" cy="291352"/>
@@ -2509,7 +2545,7 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="9401735" y="10959353"/>
+          <a:off x="9397661" y="11036776"/>
           <a:ext cx="257175" cy="228600"/>
           <a:chOff x="5939119" y="5076266"/>
           <a:chExt cx="334745" cy="291352"/>
@@ -2751,8 +2787,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="7194176" y="17716500"/>
-          <a:ext cx="257175" cy="228600"/>
+          <a:off x="7186026" y="17814297"/>
+          <a:ext cx="264307" cy="228600"/>
           <a:chOff x="5939119" y="5076266"/>
           <a:chExt cx="334745" cy="291352"/>
         </a:xfrm>
@@ -2948,7 +2984,7 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="9412941" y="17156206"/>
+          <a:off x="9408867" y="17247891"/>
           <a:ext cx="257175" cy="228600"/>
           <a:chOff x="5939119" y="5076266"/>
           <a:chExt cx="334745" cy="291352"/>
@@ -3144,7 +3180,7 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="9412940" y="7082117"/>
+          <a:off x="9408866" y="7116753"/>
           <a:ext cx="257175" cy="228600"/>
           <a:chOff x="5939119" y="5076266"/>
           <a:chExt cx="334745" cy="291352"/>
@@ -3341,7 +3377,7 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="9409579" y="8769163"/>
+          <a:off x="9405505" y="8826211"/>
           <a:ext cx="257175" cy="228600"/>
           <a:chOff x="5939119" y="5076266"/>
           <a:chExt cx="334745" cy="291352"/>
@@ -3493,7 +3529,7 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="9412940" y="15408087"/>
+          <a:off x="9408866" y="15493660"/>
           <a:ext cx="257175" cy="228600"/>
           <a:chOff x="5939119" y="5076266"/>
           <a:chExt cx="334745" cy="291352"/>
@@ -3645,7 +3681,7 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="9401735" y="9872383"/>
+          <a:off x="9397661" y="9945730"/>
           <a:ext cx="257175" cy="228600"/>
           <a:chOff x="5939119" y="5076266"/>
           <a:chExt cx="334745" cy="291352"/>
@@ -3797,7 +3833,7 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="9401735" y="10163736"/>
+          <a:off x="9397661" y="10240139"/>
           <a:ext cx="257175" cy="228600"/>
           <a:chOff x="5939119" y="5076266"/>
           <a:chExt cx="334745" cy="291352"/>
@@ -3949,7 +3985,7 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="9401735" y="11228294"/>
+          <a:off x="9397661" y="11296548"/>
           <a:ext cx="257175" cy="228600"/>
           <a:chOff x="5939119" y="5076266"/>
           <a:chExt cx="334745" cy="291352"/>
@@ -4191,7 +4227,7 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="9409579" y="9351869"/>
+          <a:off x="9405505" y="9415030"/>
           <a:ext cx="257175" cy="228600"/>
           <a:chOff x="5939119" y="5076266"/>
           <a:chExt cx="334745" cy="291352"/>
@@ -4724,7 +4760,7 @@
   <sheetPr>
     <tabColor rgb="FF92D050"/>
   </sheetPr>
-  <dimension ref="A1:P92"/>
+  <dimension ref="A1:S92"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="22.5" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="5.140625" style="12" customWidth="1"/>
@@ -4742,268 +4778,269 @@
     <col min="14" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="120"/>
-      <c r="B1" s="121"/>
-      <c r="C1" s="121"/>
-      <c r="D1" s="23" t="s">
+    <row r="1" spans="1:19" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="21"/>
+      <c r="B1" s="22"/>
+      <c r="C1" s="22"/>
+      <c r="D1" s="136" t="s">
         <v>67</v>
       </c>
-      <c r="E1" s="24"/>
-      <c r="F1" s="24"/>
-      <c r="G1" s="24"/>
-      <c r="H1" s="24"/>
-      <c r="I1" s="24"/>
-      <c r="J1" s="24"/>
-      <c r="K1" s="24"/>
-      <c r="L1" s="24"/>
-      <c r="M1" s="27" t="e" vm="1">
+      <c r="E1" s="137"/>
+      <c r="F1" s="137"/>
+      <c r="G1" s="137"/>
+      <c r="H1" s="137"/>
+      <c r="I1" s="137"/>
+      <c r="J1" s="137"/>
+      <c r="K1" s="137"/>
+      <c r="L1" s="137"/>
+      <c r="M1" s="121" t="e" vm="1">
         <v>#VALUE!</v>
       </c>
-      <c r="N1" s="28"/>
-    </row>
-    <row r="2" spans="1:16" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="122"/>
-      <c r="B2" s="123"/>
-      <c r="C2" s="123"/>
-      <c r="D2" s="25"/>
-      <c r="E2" s="25"/>
-      <c r="F2" s="25"/>
-      <c r="G2" s="25"/>
-      <c r="H2" s="25"/>
-      <c r="I2" s="25"/>
-      <c r="J2" s="25"/>
-      <c r="K2" s="25"/>
-      <c r="L2" s="25"/>
-      <c r="M2" s="29"/>
-      <c r="N2" s="30"/>
-    </row>
-    <row r="3" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="124"/>
-      <c r="B3" s="125"/>
-      <c r="C3" s="125"/>
-      <c r="D3" s="26"/>
-      <c r="E3" s="26"/>
-      <c r="F3" s="26"/>
-      <c r="G3" s="26"/>
-      <c r="H3" s="26"/>
-      <c r="I3" s="26"/>
-      <c r="J3" s="26"/>
-      <c r="K3" s="26"/>
-      <c r="L3" s="26"/>
-      <c r="M3" s="31"/>
-      <c r="N3" s="32"/>
-    </row>
-    <row r="4" spans="1:16" ht="29.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="129" t="s">
+      <c r="N1" s="122"/>
+    </row>
+    <row r="2" spans="1:19" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="23"/>
+      <c r="B2" s="24"/>
+      <c r="C2" s="24"/>
+      <c r="D2" s="138"/>
+      <c r="E2" s="138"/>
+      <c r="F2" s="138"/>
+      <c r="G2" s="138"/>
+      <c r="H2" s="138"/>
+      <c r="I2" s="138"/>
+      <c r="J2" s="138"/>
+      <c r="K2" s="138"/>
+      <c r="L2" s="138"/>
+      <c r="M2" s="123"/>
+      <c r="N2" s="124"/>
+    </row>
+    <row r="3" spans="1:19" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="25"/>
+      <c r="B3" s="26"/>
+      <c r="C3" s="26"/>
+      <c r="D3" s="139"/>
+      <c r="E3" s="139"/>
+      <c r="F3" s="139"/>
+      <c r="G3" s="139"/>
+      <c r="H3" s="139"/>
+      <c r="I3" s="139"/>
+      <c r="J3" s="139"/>
+      <c r="K3" s="139"/>
+      <c r="L3" s="139"/>
+      <c r="M3" s="125"/>
+      <c r="N3" s="126"/>
+    </row>
+    <row r="4" spans="1:19" ht="29.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="33" t="s">
         <v>0</v>
       </c>
-      <c r="B4" s="130"/>
-      <c r="C4" s="130"/>
-      <c r="D4" s="131"/>
-      <c r="E4" s="132" t="s">
+      <c r="B4" s="34"/>
+      <c r="C4" s="34"/>
+      <c r="D4" s="35"/>
+      <c r="E4" s="36" t="s">
         <v>1</v>
       </c>
-      <c r="F4" s="133"/>
-      <c r="G4" s="131"/>
-      <c r="H4" s="133" t="s">
+      <c r="F4" s="37"/>
+      <c r="G4" s="35"/>
+      <c r="H4" s="37" t="s">
         <v>81</v>
       </c>
-      <c r="I4" s="133"/>
-      <c r="J4" s="133"/>
-      <c r="K4" s="133"/>
-      <c r="L4" s="132" t="s">
+      <c r="I4" s="37"/>
+      <c r="J4" s="37"/>
+      <c r="K4" s="37"/>
+      <c r="L4" s="36" t="s">
         <v>68</v>
       </c>
-      <c r="M4" s="130"/>
-      <c r="N4" s="134"/>
+      <c r="M4" s="34"/>
+      <c r="N4" s="38"/>
       <c r="O4" s="14"/>
       <c r="P4" s="15"/>
     </row>
-    <row r="5" spans="1:16" ht="20.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="135" t="s">
+    <row r="5" spans="1:19" ht="20.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="39" t="s">
         <v>2</v>
       </c>
-      <c r="B5" s="136"/>
-      <c r="C5" s="136"/>
-      <c r="D5" s="137"/>
-      <c r="E5" s="135" t="s">
+      <c r="B5" s="40"/>
+      <c r="C5" s="40"/>
+      <c r="D5" s="41"/>
+      <c r="E5" s="39" t="s">
         <v>3</v>
       </c>
-      <c r="F5" s="136"/>
-      <c r="G5" s="136"/>
-      <c r="H5" s="137"/>
-      <c r="I5" s="138" t="s">
+      <c r="F5" s="40"/>
+      <c r="G5" s="40"/>
+      <c r="H5" s="41"/>
+      <c r="I5" s="42" t="s">
         <v>4</v>
       </c>
-      <c r="J5" s="139"/>
-      <c r="K5" s="139"/>
-      <c r="L5" s="139"/>
-      <c r="M5" s="139"/>
-      <c r="N5" s="140"/>
+      <c r="J5" s="43"/>
+      <c r="K5" s="43"/>
+      <c r="L5" s="43"/>
+      <c r="M5" s="43"/>
+      <c r="N5" s="44"/>
       <c r="O5" s="14"/>
       <c r="P5" s="15"/>
     </row>
-    <row r="6" spans="1:16" ht="33" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="20" t="s">
+    <row r="6" spans="1:19" ht="33" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="18" t="s">
         <v>5</v>
       </c>
-      <c r="B6" s="21"/>
-      <c r="C6" s="21"/>
-      <c r="D6" s="22"/>
-      <c r="E6" s="20" t="s">
+      <c r="B6" s="19"/>
+      <c r="C6" s="19"/>
+      <c r="D6" s="20"/>
+      <c r="E6" s="18" t="s">
         <v>5</v>
       </c>
-      <c r="F6" s="21"/>
-      <c r="G6" s="21"/>
-      <c r="H6" s="22"/>
-      <c r="I6" s="20" t="s">
+      <c r="F6" s="19"/>
+      <c r="G6" s="19"/>
+      <c r="H6" s="20"/>
+      <c r="I6" s="18" t="s">
         <v>5</v>
       </c>
-      <c r="J6" s="21"/>
-      <c r="K6" s="21"/>
-      <c r="L6" s="21"/>
-      <c r="M6" s="21"/>
-      <c r="N6" s="22"/>
-    </row>
-    <row r="7" spans="1:16" s="7" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="126" t="s">
+      <c r="J6" s="19"/>
+      <c r="K6" s="19"/>
+      <c r="L6" s="19"/>
+      <c r="M6" s="19"/>
+      <c r="N6" s="20"/>
+      <c r="S6" s="140"/>
+    </row>
+    <row r="7" spans="1:19" s="7" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="30" t="s">
         <v>6</v>
       </c>
-      <c r="B7" s="127"/>
-      <c r="C7" s="127"/>
-      <c r="D7" s="128"/>
-      <c r="E7" s="126" t="s">
+      <c r="B7" s="31"/>
+      <c r="C7" s="31"/>
+      <c r="D7" s="32"/>
+      <c r="E7" s="30" t="s">
         <v>6</v>
       </c>
-      <c r="F7" s="127"/>
-      <c r="G7" s="127"/>
-      <c r="H7" s="128"/>
-      <c r="I7" s="20" t="s">
+      <c r="F7" s="31"/>
+      <c r="G7" s="31"/>
+      <c r="H7" s="32"/>
+      <c r="I7" s="18" t="s">
         <v>6</v>
       </c>
-      <c r="J7" s="21"/>
-      <c r="K7" s="21"/>
-      <c r="L7" s="21"/>
-      <c r="M7" s="21"/>
-      <c r="N7" s="22"/>
-    </row>
-    <row r="8" spans="1:16" s="7" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="20" t="s">
+      <c r="J7" s="19"/>
+      <c r="K7" s="19"/>
+      <c r="L7" s="19"/>
+      <c r="M7" s="19"/>
+      <c r="N7" s="20"/>
+    </row>
+    <row r="8" spans="1:19" s="7" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="B8" s="21"/>
-      <c r="C8" s="21"/>
-      <c r="D8" s="22"/>
-      <c r="E8" s="20" t="s">
+      <c r="B8" s="19"/>
+      <c r="C8" s="19"/>
+      <c r="D8" s="20"/>
+      <c r="E8" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="F8" s="21"/>
-      <c r="G8" s="21"/>
-      <c r="H8" s="22"/>
-      <c r="I8" s="20" t="s">
+      <c r="F8" s="19"/>
+      <c r="G8" s="19"/>
+      <c r="H8" s="20"/>
+      <c r="I8" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="J8" s="21"/>
-      <c r="K8" s="21"/>
-      <c r="L8" s="21"/>
-      <c r="M8" s="21"/>
-      <c r="N8" s="22"/>
-    </row>
-    <row r="9" spans="1:16" s="7" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="20" t="s">
+      <c r="J8" s="19"/>
+      <c r="K8" s="19"/>
+      <c r="L8" s="19"/>
+      <c r="M8" s="19"/>
+      <c r="N8" s="20"/>
+    </row>
+    <row r="9" spans="1:19" s="7" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="18" t="s">
         <v>8</v>
       </c>
-      <c r="B9" s="21"/>
-      <c r="C9" s="21"/>
-      <c r="D9" s="22"/>
-      <c r="E9" s="20" t="s">
+      <c r="B9" s="19"/>
+      <c r="C9" s="19"/>
+      <c r="D9" s="20"/>
+      <c r="E9" s="18" t="s">
         <v>8</v>
       </c>
-      <c r="F9" s="21"/>
-      <c r="G9" s="21"/>
-      <c r="H9" s="22"/>
-      <c r="I9" s="20" t="s">
+      <c r="F9" s="19"/>
+      <c r="G9" s="19"/>
+      <c r="H9" s="20"/>
+      <c r="I9" s="18" t="s">
         <v>8</v>
       </c>
-      <c r="J9" s="21"/>
-      <c r="K9" s="21"/>
-      <c r="L9" s="21"/>
-      <c r="M9" s="21"/>
-      <c r="N9" s="22"/>
-    </row>
-    <row r="10" spans="1:16" s="7" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="20" t="s">
+      <c r="J9" s="19"/>
+      <c r="K9" s="19"/>
+      <c r="L9" s="19"/>
+      <c r="M9" s="19"/>
+      <c r="N9" s="20"/>
+    </row>
+    <row r="10" spans="1:19" s="7" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="18" t="s">
         <v>79</v>
       </c>
-      <c r="B10" s="21"/>
-      <c r="C10" s="21"/>
-      <c r="D10" s="22"/>
-      <c r="E10" s="20" t="s">
+      <c r="B10" s="19"/>
+      <c r="C10" s="19"/>
+      <c r="D10" s="20"/>
+      <c r="E10" s="18" t="s">
         <v>80</v>
       </c>
-      <c r="F10" s="21"/>
-      <c r="G10" s="21"/>
-      <c r="H10" s="22"/>
-      <c r="I10" s="20" t="s">
+      <c r="F10" s="19"/>
+      <c r="G10" s="19"/>
+      <c r="H10" s="20"/>
+      <c r="I10" s="18" t="s">
         <v>79</v>
       </c>
-      <c r="J10" s="21"/>
-      <c r="K10" s="21"/>
-      <c r="L10" s="21"/>
-      <c r="M10" s="21"/>
-      <c r="N10" s="22"/>
-    </row>
-    <row r="11" spans="1:16" ht="41.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="141" t="s">
+      <c r="J10" s="19"/>
+      <c r="K10" s="19"/>
+      <c r="L10" s="19"/>
+      <c r="M10" s="19"/>
+      <c r="N10" s="20"/>
+    </row>
+    <row r="11" spans="1:19" ht="41.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="45" t="s">
         <v>9</v>
       </c>
-      <c r="B11" s="142"/>
-      <c r="C11" s="142"/>
-      <c r="D11" s="142"/>
-      <c r="E11" s="142"/>
-      <c r="F11" s="142"/>
-      <c r="G11" s="142"/>
-      <c r="H11" s="142"/>
-      <c r="I11" s="142"/>
-      <c r="J11" s="142"/>
-      <c r="K11" s="142"/>
-      <c r="L11" s="142"/>
-      <c r="M11" s="142"/>
-      <c r="N11" s="143"/>
-    </row>
-    <row r="12" spans="1:16" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="118" t="s">
+      <c r="B11" s="46"/>
+      <c r="C11" s="46"/>
+      <c r="D11" s="46"/>
+      <c r="E11" s="46"/>
+      <c r="F11" s="46"/>
+      <c r="G11" s="46"/>
+      <c r="H11" s="46"/>
+      <c r="I11" s="46"/>
+      <c r="J11" s="46"/>
+      <c r="K11" s="46"/>
+      <c r="L11" s="46"/>
+      <c r="M11" s="46"/>
+      <c r="N11" s="47"/>
+    </row>
+    <row r="12" spans="1:19" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="61" t="s">
         <v>10</v>
       </c>
-      <c r="B12" s="119"/>
-      <c r="C12" s="119"/>
-      <c r="D12" s="119"/>
-      <c r="E12" s="119"/>
-      <c r="F12" s="119"/>
-      <c r="G12" s="119"/>
+      <c r="B12" s="62"/>
+      <c r="C12" s="62"/>
+      <c r="D12" s="62"/>
+      <c r="E12" s="62"/>
+      <c r="F12" s="62"/>
+      <c r="G12" s="62"/>
       <c r="H12" s="9"/>
-      <c r="I12" s="109" t="s">
+      <c r="I12" s="50" t="s">
         <v>11</v>
       </c>
-      <c r="J12" s="109"/>
-      <c r="K12" s="109"/>
-      <c r="L12" s="109"/>
-      <c r="M12" s="109"/>
-      <c r="N12" s="110"/>
-    </row>
-    <row r="13" spans="1:16" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="111" t="s">
+      <c r="J12" s="50"/>
+      <c r="K12" s="50"/>
+      <c r="L12" s="50"/>
+      <c r="M12" s="50"/>
+      <c r="N12" s="51"/>
+    </row>
+    <row r="13" spans="1:19" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="52" t="s">
         <v>12</v>
       </c>
-      <c r="B13" s="112"/>
-      <c r="C13" s="112"/>
-      <c r="D13" s="112"/>
-      <c r="E13" s="112"/>
-      <c r="F13" s="112"/>
-      <c r="G13" s="112"/>
-      <c r="H13" s="112"/>
-      <c r="I13" s="113"/>
+      <c r="B13" s="53"/>
+      <c r="C13" s="53"/>
+      <c r="D13" s="53"/>
+      <c r="E13" s="53"/>
+      <c r="F13" s="53"/>
+      <c r="G13" s="53"/>
+      <c r="H13" s="53"/>
+      <c r="I13" s="54"/>
       <c r="J13" s="11" t="s">
         <v>13</v>
       </c>
@@ -5013,1306 +5050,1306 @@
       <c r="L13" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="M13" s="114" t="s">
+      <c r="M13" s="55" t="s">
         <v>16</v>
       </c>
-      <c r="N13" s="115"/>
-    </row>
-    <row r="14" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="40" t="s">
+      <c r="N13" s="56"/>
+    </row>
+    <row r="14" spans="1:19" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="57" t="s">
         <v>17</v>
       </c>
-      <c r="B14" s="41"/>
-      <c r="C14" s="41"/>
-      <c r="D14" s="41"/>
-      <c r="E14" s="41"/>
-      <c r="F14" s="41"/>
-      <c r="G14" s="41"/>
-      <c r="H14" s="41"/>
-      <c r="I14" s="41"/>
-      <c r="J14" s="41"/>
-      <c r="K14" s="41"/>
-      <c r="L14" s="41"/>
-      <c r="M14" s="116"/>
-      <c r="N14" s="117"/>
-    </row>
-    <row r="15" spans="1:16" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B14" s="58"/>
+      <c r="C14" s="58"/>
+      <c r="D14" s="58"/>
+      <c r="E14" s="58"/>
+      <c r="F14" s="58"/>
+      <c r="G14" s="58"/>
+      <c r="H14" s="58"/>
+      <c r="I14" s="58"/>
+      <c r="J14" s="58"/>
+      <c r="K14" s="58"/>
+      <c r="L14" s="58"/>
+      <c r="M14" s="59"/>
+      <c r="N14" s="60"/>
+    </row>
+    <row r="15" spans="1:19" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="2">
         <v>1</v>
       </c>
-      <c r="B15" s="108" t="s">
+      <c r="B15" s="48" t="s">
         <v>18</v>
       </c>
-      <c r="C15" s="74"/>
-      <c r="D15" s="74"/>
-      <c r="E15" s="74"/>
-      <c r="F15" s="74"/>
-      <c r="G15" s="74"/>
-      <c r="H15" s="74"/>
-      <c r="I15" s="75"/>
+      <c r="C15" s="28"/>
+      <c r="D15" s="28"/>
+      <c r="E15" s="28"/>
+      <c r="F15" s="28"/>
+      <c r="G15" s="28"/>
+      <c r="H15" s="28"/>
+      <c r="I15" s="29"/>
       <c r="J15" s="3"/>
       <c r="K15" s="3"/>
       <c r="L15" s="3"/>
-      <c r="M15" s="36"/>
-      <c r="N15" s="37"/>
-    </row>
-    <row r="16" spans="1:16" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="M15" s="141"/>
+      <c r="N15" s="142"/>
+    </row>
+    <row r="16" spans="1:19" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="2">
         <v>2</v>
       </c>
-      <c r="B16" s="107" t="s">
+      <c r="B16" s="49" t="s">
         <v>19</v>
       </c>
-      <c r="C16" s="74"/>
-      <c r="D16" s="74"/>
-      <c r="E16" s="74"/>
-      <c r="F16" s="74"/>
-      <c r="G16" s="74"/>
-      <c r="H16" s="74"/>
-      <c r="I16" s="75"/>
+      <c r="C16" s="28"/>
+      <c r="D16" s="28"/>
+      <c r="E16" s="28"/>
+      <c r="F16" s="28"/>
+      <c r="G16" s="28"/>
+      <c r="H16" s="28"/>
+      <c r="I16" s="29"/>
       <c r="J16" s="3"/>
       <c r="K16" s="3"/>
       <c r="L16" s="3"/>
-      <c r="M16" s="36"/>
-      <c r="N16" s="37"/>
+      <c r="M16" s="141"/>
+      <c r="N16" s="142"/>
     </row>
     <row r="17" spans="1:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="2">
         <v>3</v>
       </c>
-      <c r="B17" s="108" t="s">
+      <c r="B17" s="48" t="s">
         <v>20</v>
       </c>
-      <c r="C17" s="74"/>
-      <c r="D17" s="74"/>
-      <c r="E17" s="74"/>
-      <c r="F17" s="74"/>
-      <c r="G17" s="74"/>
-      <c r="H17" s="74"/>
-      <c r="I17" s="75"/>
+      <c r="C17" s="28"/>
+      <c r="D17" s="28"/>
+      <c r="E17" s="28"/>
+      <c r="F17" s="28"/>
+      <c r="G17" s="28"/>
+      <c r="H17" s="28"/>
+      <c r="I17" s="29"/>
       <c r="J17" s="3"/>
       <c r="K17" s="3"/>
       <c r="L17" s="3"/>
-      <c r="M17" s="36"/>
-      <c r="N17" s="37"/>
+      <c r="M17" s="141"/>
+      <c r="N17" s="142"/>
     </row>
     <row r="18" spans="1:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="2">
         <v>4</v>
       </c>
-      <c r="B18" s="107" t="s">
+      <c r="B18" s="49" t="s">
         <v>21</v>
       </c>
-      <c r="C18" s="72"/>
-      <c r="D18" s="72"/>
-      <c r="E18" s="72"/>
-      <c r="F18" s="72"/>
-      <c r="G18" s="72"/>
-      <c r="H18" s="72"/>
-      <c r="I18" s="73"/>
+      <c r="C18" s="63"/>
+      <c r="D18" s="63"/>
+      <c r="E18" s="63"/>
+      <c r="F18" s="63"/>
+      <c r="G18" s="63"/>
+      <c r="H18" s="63"/>
+      <c r="I18" s="64"/>
       <c r="J18" s="3"/>
       <c r="K18" s="3"/>
       <c r="L18" s="3"/>
-      <c r="M18" s="36"/>
-      <c r="N18" s="37"/>
+      <c r="M18" s="141"/>
+      <c r="N18" s="142"/>
     </row>
     <row r="19" spans="1:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="2">
         <v>5</v>
       </c>
-      <c r="B19" s="107" t="s">
+      <c r="B19" s="49" t="s">
         <v>22</v>
       </c>
-      <c r="C19" s="72"/>
-      <c r="D19" s="72"/>
-      <c r="E19" s="72"/>
-      <c r="F19" s="72"/>
-      <c r="G19" s="72"/>
-      <c r="H19" s="72"/>
-      <c r="I19" s="73"/>
+      <c r="C19" s="63"/>
+      <c r="D19" s="63"/>
+      <c r="E19" s="63"/>
+      <c r="F19" s="63"/>
+      <c r="G19" s="63"/>
+      <c r="H19" s="63"/>
+      <c r="I19" s="64"/>
       <c r="J19" s="3"/>
       <c r="K19" s="3"/>
       <c r="L19" s="3"/>
-      <c r="M19" s="36"/>
-      <c r="N19" s="37"/>
+      <c r="M19" s="141"/>
+      <c r="N19" s="142"/>
     </row>
     <row r="20" spans="1:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="2">
         <v>6</v>
       </c>
-      <c r="B20" s="107" t="s">
+      <c r="B20" s="49" t="s">
         <v>23</v>
       </c>
-      <c r="C20" s="72"/>
-      <c r="D20" s="72"/>
-      <c r="E20" s="72"/>
-      <c r="F20" s="72"/>
-      <c r="G20" s="72"/>
-      <c r="H20" s="72"/>
-      <c r="I20" s="73"/>
+      <c r="C20" s="63"/>
+      <c r="D20" s="63"/>
+      <c r="E20" s="63"/>
+      <c r="F20" s="63"/>
+      <c r="G20" s="63"/>
+      <c r="H20" s="63"/>
+      <c r="I20" s="64"/>
       <c r="J20" s="3"/>
       <c r="K20" s="3"/>
       <c r="L20" s="3"/>
-      <c r="M20" s="36"/>
-      <c r="N20" s="37"/>
+      <c r="M20" s="141"/>
+      <c r="N20" s="142"/>
     </row>
     <row r="21" spans="1:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="2">
         <v>7</v>
       </c>
-      <c r="B21" s="107" t="s">
+      <c r="B21" s="49" t="s">
         <v>24</v>
       </c>
-      <c r="C21" s="72"/>
-      <c r="D21" s="72"/>
-      <c r="E21" s="72"/>
-      <c r="F21" s="72"/>
-      <c r="G21" s="72"/>
-      <c r="H21" s="72"/>
-      <c r="I21" s="73"/>
+      <c r="C21" s="63"/>
+      <c r="D21" s="63"/>
+      <c r="E21" s="63"/>
+      <c r="F21" s="63"/>
+      <c r="G21" s="63"/>
+      <c r="H21" s="63"/>
+      <c r="I21" s="64"/>
       <c r="J21" s="3"/>
       <c r="K21" s="3"/>
       <c r="L21" s="3"/>
-      <c r="M21" s="36"/>
-      <c r="N21" s="37"/>
+      <c r="M21" s="141"/>
+      <c r="N21" s="142"/>
     </row>
     <row r="22" spans="1:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="2">
         <v>8</v>
       </c>
-      <c r="B22" s="107" t="s">
+      <c r="B22" s="49" t="s">
         <v>25</v>
       </c>
-      <c r="C22" s="72"/>
-      <c r="D22" s="72"/>
-      <c r="E22" s="72"/>
-      <c r="F22" s="72"/>
-      <c r="G22" s="72"/>
-      <c r="H22" s="72"/>
-      <c r="I22" s="73"/>
+      <c r="C22" s="63"/>
+      <c r="D22" s="63"/>
+      <c r="E22" s="63"/>
+      <c r="F22" s="63"/>
+      <c r="G22" s="63"/>
+      <c r="H22" s="63"/>
+      <c r="I22" s="64"/>
       <c r="J22" s="3"/>
       <c r="K22" s="3"/>
       <c r="L22" s="3"/>
-      <c r="M22" s="36"/>
-      <c r="N22" s="37"/>
+      <c r="M22" s="141"/>
+      <c r="N22" s="142"/>
     </row>
     <row r="23" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="40" t="s">
+      <c r="A23" s="57" t="s">
         <v>26</v>
       </c>
-      <c r="B23" s="41"/>
-      <c r="C23" s="41"/>
-      <c r="D23" s="41"/>
-      <c r="E23" s="41"/>
-      <c r="F23" s="41"/>
-      <c r="G23" s="41"/>
-      <c r="H23" s="41"/>
-      <c r="I23" s="41"/>
-      <c r="J23" s="41"/>
-      <c r="K23" s="41"/>
-      <c r="L23" s="41"/>
-      <c r="M23" s="41"/>
-      <c r="N23" s="42"/>
+      <c r="B23" s="58"/>
+      <c r="C23" s="58"/>
+      <c r="D23" s="58"/>
+      <c r="E23" s="58"/>
+      <c r="F23" s="58"/>
+      <c r="G23" s="58"/>
+      <c r="H23" s="58"/>
+      <c r="I23" s="58"/>
+      <c r="J23" s="58"/>
+      <c r="K23" s="58"/>
+      <c r="L23" s="58"/>
+      <c r="M23" s="58"/>
+      <c r="N23" s="65"/>
     </row>
     <row r="24" spans="1:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="4">
         <v>9</v>
       </c>
-      <c r="B24" s="54" t="s">
+      <c r="B24" s="66" t="s">
         <v>27</v>
       </c>
-      <c r="C24" s="55"/>
-      <c r="D24" s="55"/>
-      <c r="E24" s="55"/>
-      <c r="F24" s="55"/>
-      <c r="G24" s="55"/>
-      <c r="H24" s="55"/>
-      <c r="I24" s="56"/>
+      <c r="C24" s="67"/>
+      <c r="D24" s="67"/>
+      <c r="E24" s="67"/>
+      <c r="F24" s="67"/>
+      <c r="G24" s="67"/>
+      <c r="H24" s="67"/>
+      <c r="I24" s="68"/>
       <c r="J24" s="5"/>
       <c r="K24" s="5"/>
       <c r="L24" s="5"/>
-      <c r="M24" s="36"/>
-      <c r="N24" s="37"/>
+      <c r="M24" s="141"/>
+      <c r="N24" s="142"/>
     </row>
     <row r="25" spans="1:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="4">
         <v>10</v>
       </c>
-      <c r="B25" s="54" t="s">
+      <c r="B25" s="66" t="s">
         <v>28</v>
       </c>
-      <c r="C25" s="55"/>
-      <c r="D25" s="55"/>
-      <c r="E25" s="55"/>
-      <c r="F25" s="55"/>
-      <c r="G25" s="55"/>
-      <c r="H25" s="55"/>
-      <c r="I25" s="56"/>
+      <c r="C25" s="67"/>
+      <c r="D25" s="67"/>
+      <c r="E25" s="67"/>
+      <c r="F25" s="67"/>
+      <c r="G25" s="67"/>
+      <c r="H25" s="67"/>
+      <c r="I25" s="68"/>
       <c r="J25" s="5"/>
       <c r="K25" s="5"/>
       <c r="L25" s="5"/>
-      <c r="M25" s="36"/>
-      <c r="N25" s="37"/>
+      <c r="M25" s="141"/>
+      <c r="N25" s="142"/>
     </row>
     <row r="26" spans="1:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="4">
         <v>11</v>
       </c>
-      <c r="B26" s="54" t="s">
+      <c r="B26" s="66" t="s">
         <v>53</v>
       </c>
-      <c r="C26" s="55"/>
-      <c r="D26" s="55"/>
-      <c r="E26" s="55"/>
-      <c r="F26" s="55"/>
-      <c r="G26" s="55"/>
-      <c r="H26" s="55"/>
-      <c r="I26" s="56"/>
+      <c r="C26" s="67"/>
+      <c r="D26" s="67"/>
+      <c r="E26" s="67"/>
+      <c r="F26" s="67"/>
+      <c r="G26" s="67"/>
+      <c r="H26" s="67"/>
+      <c r="I26" s="68"/>
       <c r="J26" s="5"/>
       <c r="K26" s="5"/>
       <c r="L26" s="5"/>
-      <c r="M26" s="36"/>
-      <c r="N26" s="37"/>
+      <c r="M26" s="141"/>
+      <c r="N26" s="142"/>
     </row>
     <row r="27" spans="1:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="4">
         <v>12</v>
       </c>
-      <c r="B27" s="49" t="s">
+      <c r="B27" s="27" t="s">
         <v>29</v>
       </c>
-      <c r="C27" s="52"/>
-      <c r="D27" s="52"/>
-      <c r="E27" s="52"/>
-      <c r="F27" s="52"/>
-      <c r="G27" s="52"/>
-      <c r="H27" s="52"/>
-      <c r="I27" s="53"/>
+      <c r="C27" s="134"/>
+      <c r="D27" s="134"/>
+      <c r="E27" s="134"/>
+      <c r="F27" s="134"/>
+      <c r="G27" s="134"/>
+      <c r="H27" s="134"/>
+      <c r="I27" s="135"/>
       <c r="J27" s="5"/>
       <c r="K27" s="5"/>
       <c r="L27" s="5"/>
-      <c r="M27" s="36"/>
-      <c r="N27" s="37"/>
+      <c r="M27" s="141"/>
+      <c r="N27" s="142"/>
     </row>
     <row r="28" spans="1:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="4">
         <v>13</v>
       </c>
-      <c r="B28" s="33" t="s">
+      <c r="B28" s="69" t="s">
         <v>52</v>
       </c>
-      <c r="C28" s="38"/>
-      <c r="D28" s="38"/>
-      <c r="E28" s="38"/>
-      <c r="F28" s="38"/>
-      <c r="G28" s="38"/>
-      <c r="H28" s="38"/>
-      <c r="I28" s="39"/>
+      <c r="C28" s="127"/>
+      <c r="D28" s="127"/>
+      <c r="E28" s="127"/>
+      <c r="F28" s="127"/>
+      <c r="G28" s="127"/>
+      <c r="H28" s="127"/>
+      <c r="I28" s="128"/>
       <c r="J28" s="3"/>
       <c r="K28" s="3"/>
       <c r="L28" s="3"/>
-      <c r="M28" s="36"/>
-      <c r="N28" s="37"/>
+      <c r="M28" s="141"/>
+      <c r="N28" s="142"/>
     </row>
     <row r="29" spans="1:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="4">
         <v>14</v>
       </c>
-      <c r="B29" s="33" t="s">
+      <c r="B29" s="69" t="s">
         <v>30</v>
       </c>
-      <c r="C29" s="34"/>
-      <c r="D29" s="34"/>
-      <c r="E29" s="34"/>
-      <c r="F29" s="34"/>
-      <c r="G29" s="34"/>
-      <c r="H29" s="34"/>
-      <c r="I29" s="35"/>
+      <c r="C29" s="73"/>
+      <c r="D29" s="73"/>
+      <c r="E29" s="73"/>
+      <c r="F29" s="73"/>
+      <c r="G29" s="73"/>
+      <c r="H29" s="73"/>
+      <c r="I29" s="74"/>
       <c r="J29" s="3"/>
       <c r="K29" s="3"/>
       <c r="L29" s="3"/>
-      <c r="M29" s="36"/>
-      <c r="N29" s="37"/>
+      <c r="M29" s="141"/>
+      <c r="N29" s="142"/>
     </row>
     <row r="30" spans="1:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="4">
         <v>15</v>
       </c>
-      <c r="B30" s="33" t="s">
+      <c r="B30" s="69" t="s">
         <v>31</v>
       </c>
-      <c r="C30" s="38"/>
-      <c r="D30" s="38"/>
-      <c r="E30" s="38"/>
-      <c r="F30" s="38"/>
-      <c r="G30" s="38"/>
-      <c r="H30" s="38"/>
-      <c r="I30" s="39"/>
+      <c r="C30" s="127"/>
+      <c r="D30" s="127"/>
+      <c r="E30" s="127"/>
+      <c r="F30" s="127"/>
+      <c r="G30" s="127"/>
+      <c r="H30" s="127"/>
+      <c r="I30" s="128"/>
       <c r="J30" s="3"/>
       <c r="K30" s="3"/>
       <c r="L30" s="3"/>
-      <c r="M30" s="36"/>
-      <c r="N30" s="37"/>
+      <c r="M30" s="141"/>
+      <c r="N30" s="142"/>
     </row>
     <row r="31" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="40" t="s">
+      <c r="A31" s="57" t="s">
         <v>72</v>
       </c>
-      <c r="B31" s="41"/>
-      <c r="C31" s="41"/>
-      <c r="D31" s="41"/>
-      <c r="E31" s="41"/>
-      <c r="F31" s="41"/>
-      <c r="G31" s="41"/>
-      <c r="H31" s="41"/>
-      <c r="I31" s="41"/>
-      <c r="J31" s="41"/>
-      <c r="K31" s="41"/>
-      <c r="L31" s="41"/>
-      <c r="M31" s="41"/>
-      <c r="N31" s="42"/>
+      <c r="B31" s="58"/>
+      <c r="C31" s="58"/>
+      <c r="D31" s="58"/>
+      <c r="E31" s="58"/>
+      <c r="F31" s="58"/>
+      <c r="G31" s="58"/>
+      <c r="H31" s="58"/>
+      <c r="I31" s="58"/>
+      <c r="J31" s="58"/>
+      <c r="K31" s="58"/>
+      <c r="L31" s="58"/>
+      <c r="M31" s="58"/>
+      <c r="N31" s="65"/>
     </row>
     <row r="32" spans="1:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="2">
         <v>16</v>
       </c>
-      <c r="B32" s="33" t="s">
+      <c r="B32" s="69" t="s">
         <v>54</v>
       </c>
-      <c r="C32" s="34"/>
-      <c r="D32" s="34"/>
-      <c r="E32" s="34"/>
-      <c r="F32" s="34"/>
-      <c r="G32" s="34"/>
-      <c r="H32" s="34"/>
-      <c r="I32" s="35"/>
+      <c r="C32" s="73"/>
+      <c r="D32" s="73"/>
+      <c r="E32" s="73"/>
+      <c r="F32" s="73"/>
+      <c r="G32" s="73"/>
+      <c r="H32" s="73"/>
+      <c r="I32" s="74"/>
       <c r="J32" s="3"/>
       <c r="K32" s="3"/>
       <c r="L32" s="3"/>
-      <c r="M32" s="36"/>
-      <c r="N32" s="37"/>
+      <c r="M32" s="141"/>
+      <c r="N32" s="142"/>
     </row>
     <row r="33" spans="1:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A33" s="2">
         <v>17</v>
       </c>
-      <c r="B33" s="46" t="s">
+      <c r="B33" s="129" t="s">
         <v>55</v>
       </c>
-      <c r="C33" s="47"/>
-      <c r="D33" s="47"/>
-      <c r="E33" s="47"/>
-      <c r="F33" s="47"/>
-      <c r="G33" s="47"/>
-      <c r="H33" s="47"/>
-      <c r="I33" s="48"/>
+      <c r="C33" s="130"/>
+      <c r="D33" s="130"/>
+      <c r="E33" s="130"/>
+      <c r="F33" s="130"/>
+      <c r="G33" s="130"/>
+      <c r="H33" s="130"/>
+      <c r="I33" s="131"/>
       <c r="J33" s="5"/>
       <c r="K33" s="5"/>
       <c r="L33" s="5"/>
-      <c r="M33" s="36"/>
-      <c r="N33" s="37"/>
+      <c r="M33" s="141"/>
+      <c r="N33" s="142"/>
     </row>
     <row r="34" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="43" t="s">
+      <c r="A34" s="70" t="s">
         <v>73</v>
       </c>
-      <c r="B34" s="44"/>
-      <c r="C34" s="44"/>
-      <c r="D34" s="44"/>
-      <c r="E34" s="44"/>
-      <c r="F34" s="44"/>
-      <c r="G34" s="44"/>
-      <c r="H34" s="44"/>
-      <c r="I34" s="44"/>
-      <c r="J34" s="44"/>
-      <c r="K34" s="44"/>
-      <c r="L34" s="44"/>
-      <c r="M34" s="44"/>
-      <c r="N34" s="45"/>
+      <c r="B34" s="71"/>
+      <c r="C34" s="71"/>
+      <c r="D34" s="71"/>
+      <c r="E34" s="71"/>
+      <c r="F34" s="71"/>
+      <c r="G34" s="71"/>
+      <c r="H34" s="71"/>
+      <c r="I34" s="71"/>
+      <c r="J34" s="71"/>
+      <c r="K34" s="71"/>
+      <c r="L34" s="71"/>
+      <c r="M34" s="71"/>
+      <c r="N34" s="72"/>
     </row>
     <row r="35" spans="1:14" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="2">
         <v>18</v>
       </c>
-      <c r="B35" s="49" t="s">
+      <c r="B35" s="27" t="s">
         <v>56</v>
       </c>
-      <c r="C35" s="50"/>
-      <c r="D35" s="50"/>
-      <c r="E35" s="50"/>
-      <c r="F35" s="50"/>
-      <c r="G35" s="50"/>
-      <c r="H35" s="50"/>
-      <c r="I35" s="51"/>
+      <c r="C35" s="132"/>
+      <c r="D35" s="132"/>
+      <c r="E35" s="132"/>
+      <c r="F35" s="132"/>
+      <c r="G35" s="132"/>
+      <c r="H35" s="132"/>
+      <c r="I35" s="133"/>
       <c r="J35" s="3"/>
       <c r="K35" s="3"/>
       <c r="L35" s="3"/>
-      <c r="M35" s="36"/>
-      <c r="N35" s="37"/>
+      <c r="M35" s="141"/>
+      <c r="N35" s="142"/>
     </row>
     <row r="36" spans="1:14" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="2">
         <v>19</v>
       </c>
-      <c r="B36" s="33" t="s">
+      <c r="B36" s="69" t="s">
         <v>57</v>
       </c>
-      <c r="C36" s="34"/>
-      <c r="D36" s="34"/>
-      <c r="E36" s="34"/>
-      <c r="F36" s="34"/>
-      <c r="G36" s="34"/>
-      <c r="H36" s="34"/>
-      <c r="I36" s="35"/>
+      <c r="C36" s="73"/>
+      <c r="D36" s="73"/>
+      <c r="E36" s="73"/>
+      <c r="F36" s="73"/>
+      <c r="G36" s="73"/>
+      <c r="H36" s="73"/>
+      <c r="I36" s="74"/>
       <c r="J36" s="3"/>
       <c r="K36" s="3"/>
       <c r="L36" s="3"/>
-      <c r="M36" s="36"/>
-      <c r="N36" s="37"/>
+      <c r="M36" s="141"/>
+      <c r="N36" s="142"/>
     </row>
     <row r="37" spans="1:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="2">
         <v>20</v>
       </c>
-      <c r="B37" s="33" t="s">
+      <c r="B37" s="69" t="s">
         <v>32</v>
       </c>
-      <c r="C37" s="72"/>
-      <c r="D37" s="72"/>
-      <c r="E37" s="72"/>
-      <c r="F37" s="72"/>
-      <c r="G37" s="72"/>
-      <c r="H37" s="72"/>
-      <c r="I37" s="73"/>
+      <c r="C37" s="63"/>
+      <c r="D37" s="63"/>
+      <c r="E37" s="63"/>
+      <c r="F37" s="63"/>
+      <c r="G37" s="63"/>
+      <c r="H37" s="63"/>
+      <c r="I37" s="64"/>
       <c r="J37" s="3"/>
       <c r="K37" s="3"/>
       <c r="L37" s="3"/>
-      <c r="M37" s="36"/>
-      <c r="N37" s="37"/>
+      <c r="M37" s="141"/>
+      <c r="N37" s="142"/>
     </row>
     <row r="38" spans="1:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="2">
         <v>21</v>
       </c>
-      <c r="B38" s="33" t="s">
+      <c r="B38" s="69" t="s">
         <v>58</v>
       </c>
-      <c r="C38" s="72"/>
-      <c r="D38" s="72"/>
-      <c r="E38" s="72"/>
-      <c r="F38" s="72"/>
-      <c r="G38" s="72"/>
-      <c r="H38" s="72"/>
-      <c r="I38" s="73"/>
+      <c r="C38" s="63"/>
+      <c r="D38" s="63"/>
+      <c r="E38" s="63"/>
+      <c r="F38" s="63"/>
+      <c r="G38" s="63"/>
+      <c r="H38" s="63"/>
+      <c r="I38" s="64"/>
       <c r="J38" s="3"/>
       <c r="K38" s="3"/>
       <c r="L38" s="3"/>
-      <c r="M38" s="36"/>
-      <c r="N38" s="37"/>
+      <c r="M38" s="141"/>
+      <c r="N38" s="142"/>
     </row>
     <row r="39" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="43" t="s">
+      <c r="A39" s="70" t="s">
         <v>74</v>
       </c>
-      <c r="B39" s="44"/>
-      <c r="C39" s="44"/>
-      <c r="D39" s="44"/>
-      <c r="E39" s="44"/>
-      <c r="F39" s="44"/>
-      <c r="G39" s="44"/>
-      <c r="H39" s="44"/>
-      <c r="I39" s="44"/>
-      <c r="J39" s="44"/>
-      <c r="K39" s="44"/>
-      <c r="L39" s="44"/>
-      <c r="M39" s="44"/>
-      <c r="N39" s="45"/>
+      <c r="B39" s="71"/>
+      <c r="C39" s="71"/>
+      <c r="D39" s="71"/>
+      <c r="E39" s="71"/>
+      <c r="F39" s="71"/>
+      <c r="G39" s="71"/>
+      <c r="H39" s="71"/>
+      <c r="I39" s="71"/>
+      <c r="J39" s="71"/>
+      <c r="K39" s="71"/>
+      <c r="L39" s="71"/>
+      <c r="M39" s="71"/>
+      <c r="N39" s="72"/>
     </row>
     <row r="40" spans="1:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="2">
         <v>22</v>
       </c>
-      <c r="B40" s="49" t="s">
+      <c r="B40" s="27" t="s">
         <v>33</v>
       </c>
-      <c r="C40" s="74"/>
-      <c r="D40" s="74"/>
-      <c r="E40" s="74"/>
-      <c r="F40" s="74"/>
-      <c r="G40" s="74"/>
-      <c r="H40" s="74"/>
-      <c r="I40" s="75"/>
+      <c r="C40" s="28"/>
+      <c r="D40" s="28"/>
+      <c r="E40" s="28"/>
+      <c r="F40" s="28"/>
+      <c r="G40" s="28"/>
+      <c r="H40" s="28"/>
+      <c r="I40" s="29"/>
       <c r="J40" s="3"/>
       <c r="K40" s="3"/>
       <c r="L40" s="3"/>
-      <c r="M40" s="18"/>
-      <c r="N40" s="19"/>
+      <c r="M40" s="143"/>
+      <c r="N40" s="144"/>
     </row>
     <row r="41" spans="1:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" s="2">
         <v>23</v>
       </c>
-      <c r="B41" s="49" t="s">
+      <c r="B41" s="27" t="s">
         <v>66</v>
       </c>
-      <c r="C41" s="74"/>
-      <c r="D41" s="74"/>
-      <c r="E41" s="74"/>
-      <c r="F41" s="74"/>
-      <c r="G41" s="74"/>
-      <c r="H41" s="74"/>
-      <c r="I41" s="75"/>
+      <c r="C41" s="28"/>
+      <c r="D41" s="28"/>
+      <c r="E41" s="28"/>
+      <c r="F41" s="28"/>
+      <c r="G41" s="28"/>
+      <c r="H41" s="28"/>
+      <c r="I41" s="29"/>
       <c r="J41" s="3"/>
       <c r="K41" s="3"/>
       <c r="L41" s="3"/>
-      <c r="M41" s="18"/>
-      <c r="N41" s="19"/>
+      <c r="M41" s="143"/>
+      <c r="N41" s="144"/>
     </row>
     <row r="42" spans="1:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" s="2">
         <v>24</v>
       </c>
-      <c r="B42" s="49" t="s">
+      <c r="B42" s="27" t="s">
         <v>59</v>
       </c>
-      <c r="C42" s="74"/>
-      <c r="D42" s="74"/>
-      <c r="E42" s="74"/>
-      <c r="F42" s="74"/>
-      <c r="G42" s="74"/>
-      <c r="H42" s="74"/>
-      <c r="I42" s="75"/>
+      <c r="C42" s="28"/>
+      <c r="D42" s="28"/>
+      <c r="E42" s="28"/>
+      <c r="F42" s="28"/>
+      <c r="G42" s="28"/>
+      <c r="H42" s="28"/>
+      <c r="I42" s="29"/>
       <c r="J42" s="3"/>
       <c r="K42" s="3"/>
       <c r="L42" s="3"/>
-      <c r="M42" s="18"/>
-      <c r="N42" s="19"/>
+      <c r="M42" s="143"/>
+      <c r="N42" s="144"/>
     </row>
     <row r="43" spans="1:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" s="2">
         <v>25</v>
       </c>
-      <c r="B43" s="49" t="s">
+      <c r="B43" s="27" t="s">
         <v>34</v>
       </c>
-      <c r="C43" s="74"/>
-      <c r="D43" s="74"/>
-      <c r="E43" s="74"/>
-      <c r="F43" s="74"/>
-      <c r="G43" s="74"/>
-      <c r="H43" s="74"/>
-      <c r="I43" s="75"/>
+      <c r="C43" s="28"/>
+      <c r="D43" s="28"/>
+      <c r="E43" s="28"/>
+      <c r="F43" s="28"/>
+      <c r="G43" s="28"/>
+      <c r="H43" s="28"/>
+      <c r="I43" s="29"/>
       <c r="J43" s="3"/>
       <c r="K43" s="3"/>
       <c r="L43" s="3"/>
-      <c r="M43" s="36"/>
-      <c r="N43" s="37"/>
+      <c r="M43" s="141"/>
+      <c r="N43" s="142"/>
     </row>
     <row r="44" spans="1:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" s="2">
         <v>26</v>
       </c>
-      <c r="B44" s="49" t="s">
+      <c r="B44" s="27" t="s">
         <v>60</v>
       </c>
-      <c r="C44" s="74"/>
-      <c r="D44" s="74"/>
-      <c r="E44" s="74"/>
-      <c r="F44" s="74"/>
-      <c r="G44" s="74"/>
-      <c r="H44" s="74"/>
-      <c r="I44" s="75"/>
+      <c r="C44" s="28"/>
+      <c r="D44" s="28"/>
+      <c r="E44" s="28"/>
+      <c r="F44" s="28"/>
+      <c r="G44" s="28"/>
+      <c r="H44" s="28"/>
+      <c r="I44" s="29"/>
       <c r="J44" s="3"/>
       <c r="K44" s="3"/>
       <c r="L44" s="3"/>
-      <c r="M44" s="36"/>
-      <c r="N44" s="37"/>
+      <c r="M44" s="141"/>
+      <c r="N44" s="142"/>
     </row>
     <row r="45" spans="1:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A45" s="2">
         <v>27</v>
       </c>
-      <c r="B45" s="49" t="s">
+      <c r="B45" s="27" t="s">
         <v>35</v>
       </c>
-      <c r="C45" s="74"/>
-      <c r="D45" s="74"/>
-      <c r="E45" s="74"/>
-      <c r="F45" s="74"/>
-      <c r="G45" s="74"/>
-      <c r="H45" s="74"/>
-      <c r="I45" s="75"/>
+      <c r="C45" s="28"/>
+      <c r="D45" s="28"/>
+      <c r="E45" s="28"/>
+      <c r="F45" s="28"/>
+      <c r="G45" s="28"/>
+      <c r="H45" s="28"/>
+      <c r="I45" s="29"/>
       <c r="J45" s="3"/>
       <c r="K45" s="3"/>
       <c r="L45" s="3"/>
-      <c r="M45" s="36"/>
-      <c r="N45" s="37"/>
+      <c r="M45" s="141"/>
+      <c r="N45" s="142"/>
     </row>
     <row r="46" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A46" s="43" t="s">
+      <c r="A46" s="70" t="s">
         <v>75</v>
       </c>
-      <c r="B46" s="44"/>
-      <c r="C46" s="44"/>
-      <c r="D46" s="44"/>
-      <c r="E46" s="44"/>
-      <c r="F46" s="44"/>
-      <c r="G46" s="44"/>
-      <c r="H46" s="44"/>
-      <c r="I46" s="44"/>
-      <c r="J46" s="44"/>
-      <c r="K46" s="44"/>
-      <c r="L46" s="44"/>
-      <c r="M46" s="44"/>
-      <c r="N46" s="45"/>
+      <c r="B46" s="71"/>
+      <c r="C46" s="71"/>
+      <c r="D46" s="71"/>
+      <c r="E46" s="71"/>
+      <c r="F46" s="71"/>
+      <c r="G46" s="71"/>
+      <c r="H46" s="71"/>
+      <c r="I46" s="71"/>
+      <c r="J46" s="71"/>
+      <c r="K46" s="71"/>
+      <c r="L46" s="71"/>
+      <c r="M46" s="71"/>
+      <c r="N46" s="72"/>
     </row>
     <row r="47" spans="1:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A47" s="2">
         <v>28</v>
       </c>
-      <c r="B47" s="33" t="s">
+      <c r="B47" s="69" t="s">
         <v>61</v>
       </c>
-      <c r="C47" s="74"/>
-      <c r="D47" s="74"/>
-      <c r="E47" s="74"/>
-      <c r="F47" s="74"/>
-      <c r="G47" s="74"/>
-      <c r="H47" s="74"/>
-      <c r="I47" s="75"/>
+      <c r="C47" s="28"/>
+      <c r="D47" s="28"/>
+      <c r="E47" s="28"/>
+      <c r="F47" s="28"/>
+      <c r="G47" s="28"/>
+      <c r="H47" s="28"/>
+      <c r="I47" s="29"/>
       <c r="J47" s="3"/>
       <c r="K47" s="3"/>
       <c r="L47" s="3"/>
-      <c r="M47" s="36"/>
-      <c r="N47" s="37"/>
+      <c r="M47" s="141"/>
+      <c r="N47" s="142"/>
     </row>
     <row r="48" spans="1:14" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A48" s="2">
         <v>29</v>
       </c>
-      <c r="B48" s="33" t="s">
+      <c r="B48" s="69" t="s">
         <v>62</v>
       </c>
-      <c r="C48" s="34"/>
-      <c r="D48" s="34"/>
-      <c r="E48" s="34"/>
-      <c r="F48" s="34"/>
-      <c r="G48" s="34"/>
-      <c r="H48" s="34"/>
-      <c r="I48" s="35"/>
+      <c r="C48" s="73"/>
+      <c r="D48" s="73"/>
+      <c r="E48" s="73"/>
+      <c r="F48" s="73"/>
+      <c r="G48" s="73"/>
+      <c r="H48" s="73"/>
+      <c r="I48" s="74"/>
       <c r="J48" s="3"/>
       <c r="K48" s="3"/>
       <c r="L48" s="3"/>
-      <c r="M48" s="36"/>
-      <c r="N48" s="37"/>
+      <c r="M48" s="141"/>
+      <c r="N48" s="142"/>
     </row>
     <row r="49" spans="1:14" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A49" s="2">
         <v>30</v>
       </c>
-      <c r="B49" s="49" t="s">
+      <c r="B49" s="27" t="s">
         <v>36</v>
       </c>
-      <c r="C49" s="74"/>
-      <c r="D49" s="74"/>
-      <c r="E49" s="74"/>
-      <c r="F49" s="74"/>
-      <c r="G49" s="74"/>
-      <c r="H49" s="74"/>
-      <c r="I49" s="75"/>
+      <c r="C49" s="28"/>
+      <c r="D49" s="28"/>
+      <c r="E49" s="28"/>
+      <c r="F49" s="28"/>
+      <c r="G49" s="28"/>
+      <c r="H49" s="28"/>
+      <c r="I49" s="29"/>
       <c r="J49" s="3"/>
       <c r="K49" s="3"/>
       <c r="L49" s="3"/>
-      <c r="M49" s="36"/>
-      <c r="N49" s="37"/>
+      <c r="M49" s="141"/>
+      <c r="N49" s="142"/>
     </row>
     <row r="50" spans="1:14" ht="21" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A50" s="40" t="s">
+      <c r="A50" s="57" t="s">
         <v>76</v>
       </c>
-      <c r="B50" s="41"/>
-      <c r="C50" s="41"/>
-      <c r="D50" s="41"/>
-      <c r="E50" s="41"/>
-      <c r="F50" s="41"/>
-      <c r="G50" s="41"/>
-      <c r="H50" s="41"/>
-      <c r="I50" s="41"/>
-      <c r="J50" s="41"/>
-      <c r="K50" s="41"/>
-      <c r="L50" s="41"/>
-      <c r="M50" s="41"/>
-      <c r="N50" s="42"/>
+      <c r="B50" s="58"/>
+      <c r="C50" s="58"/>
+      <c r="D50" s="58"/>
+      <c r="E50" s="58"/>
+      <c r="F50" s="58"/>
+      <c r="G50" s="58"/>
+      <c r="H50" s="58"/>
+      <c r="I50" s="58"/>
+      <c r="J50" s="58"/>
+      <c r="K50" s="58"/>
+      <c r="L50" s="58"/>
+      <c r="M50" s="58"/>
+      <c r="N50" s="65"/>
     </row>
     <row r="51" spans="1:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A51" s="4">
         <v>31</v>
       </c>
-      <c r="B51" s="33" t="s">
+      <c r="B51" s="69" t="s">
         <v>37</v>
       </c>
-      <c r="C51" s="72"/>
-      <c r="D51" s="72"/>
-      <c r="E51" s="72"/>
-      <c r="F51" s="72"/>
-      <c r="G51" s="72"/>
-      <c r="H51" s="72"/>
-      <c r="I51" s="73"/>
+      <c r="C51" s="63"/>
+      <c r="D51" s="63"/>
+      <c r="E51" s="63"/>
+      <c r="F51" s="63"/>
+      <c r="G51" s="63"/>
+      <c r="H51" s="63"/>
+      <c r="I51" s="64"/>
       <c r="J51" s="3"/>
       <c r="K51" s="3"/>
       <c r="L51" s="3"/>
-      <c r="M51" s="36"/>
-      <c r="N51" s="37"/>
+      <c r="M51" s="141"/>
+      <c r="N51" s="142"/>
     </row>
     <row r="52" spans="1:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A52" s="4">
         <v>32</v>
       </c>
-      <c r="B52" s="33" t="s">
+      <c r="B52" s="69" t="s">
         <v>38</v>
       </c>
-      <c r="C52" s="72"/>
-      <c r="D52" s="72"/>
-      <c r="E52" s="72"/>
-      <c r="F52" s="72"/>
-      <c r="G52" s="72"/>
-      <c r="H52" s="72"/>
-      <c r="I52" s="73"/>
+      <c r="C52" s="63"/>
+      <c r="D52" s="63"/>
+      <c r="E52" s="63"/>
+      <c r="F52" s="63"/>
+      <c r="G52" s="63"/>
+      <c r="H52" s="63"/>
+      <c r="I52" s="64"/>
       <c r="J52" s="3"/>
       <c r="K52" s="3"/>
       <c r="L52" s="3"/>
-      <c r="M52" s="36"/>
-      <c r="N52" s="37"/>
+      <c r="M52" s="141"/>
+      <c r="N52" s="142"/>
     </row>
     <row r="53" spans="1:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A53" s="4">
         <v>33</v>
       </c>
-      <c r="B53" s="49" t="s">
+      <c r="B53" s="27" t="s">
         <v>63</v>
       </c>
-      <c r="C53" s="74"/>
-      <c r="D53" s="74"/>
-      <c r="E53" s="74"/>
-      <c r="F53" s="74"/>
-      <c r="G53" s="74"/>
-      <c r="H53" s="74"/>
-      <c r="I53" s="75"/>
+      <c r="C53" s="28"/>
+      <c r="D53" s="28"/>
+      <c r="E53" s="28"/>
+      <c r="F53" s="28"/>
+      <c r="G53" s="28"/>
+      <c r="H53" s="28"/>
+      <c r="I53" s="29"/>
       <c r="J53" s="3"/>
       <c r="K53" s="3"/>
       <c r="L53" s="3"/>
-      <c r="M53" s="36"/>
-      <c r="N53" s="37"/>
+      <c r="M53" s="141"/>
+      <c r="N53" s="142"/>
     </row>
     <row r="54" spans="1:14" ht="21" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A54" s="40" t="s">
+      <c r="A54" s="57" t="s">
         <v>77</v>
       </c>
-      <c r="B54" s="41"/>
-      <c r="C54" s="41"/>
-      <c r="D54" s="41"/>
-      <c r="E54" s="41"/>
-      <c r="F54" s="41"/>
-      <c r="G54" s="41"/>
-      <c r="H54" s="41"/>
-      <c r="I54" s="41"/>
-      <c r="J54" s="41"/>
-      <c r="K54" s="41"/>
-      <c r="L54" s="41"/>
-      <c r="M54" s="41"/>
-      <c r="N54" s="42"/>
+      <c r="B54" s="58"/>
+      <c r="C54" s="58"/>
+      <c r="D54" s="58"/>
+      <c r="E54" s="58"/>
+      <c r="F54" s="58"/>
+      <c r="G54" s="58"/>
+      <c r="H54" s="58"/>
+      <c r="I54" s="58"/>
+      <c r="J54" s="58"/>
+      <c r="K54" s="58"/>
+      <c r="L54" s="58"/>
+      <c r="M54" s="58"/>
+      <c r="N54" s="65"/>
     </row>
     <row r="55" spans="1:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A55" s="4">
         <v>34</v>
       </c>
-      <c r="B55" s="49" t="s">
+      <c r="B55" s="27" t="s">
         <v>64</v>
       </c>
-      <c r="C55" s="74"/>
-      <c r="D55" s="74"/>
-      <c r="E55" s="74"/>
-      <c r="F55" s="74"/>
-      <c r="G55" s="74"/>
-      <c r="H55" s="74"/>
-      <c r="I55" s="75"/>
+      <c r="C55" s="28"/>
+      <c r="D55" s="28"/>
+      <c r="E55" s="28"/>
+      <c r="F55" s="28"/>
+      <c r="G55" s="28"/>
+      <c r="H55" s="28"/>
+      <c r="I55" s="29"/>
       <c r="J55" s="3"/>
       <c r="K55" s="3"/>
       <c r="L55" s="3"/>
-      <c r="M55" s="36"/>
-      <c r="N55" s="37"/>
+      <c r="M55" s="141"/>
+      <c r="N55" s="142"/>
     </row>
     <row r="56" spans="1:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A56" s="4">
         <v>35</v>
       </c>
-      <c r="B56" s="33" t="s">
+      <c r="B56" s="69" t="s">
         <v>65</v>
       </c>
-      <c r="C56" s="72"/>
-      <c r="D56" s="72"/>
-      <c r="E56" s="72"/>
-      <c r="F56" s="72"/>
-      <c r="G56" s="72"/>
-      <c r="H56" s="72"/>
-      <c r="I56" s="73"/>
+      <c r="C56" s="63"/>
+      <c r="D56" s="63"/>
+      <c r="E56" s="63"/>
+      <c r="F56" s="63"/>
+      <c r="G56" s="63"/>
+      <c r="H56" s="63"/>
+      <c r="I56" s="64"/>
       <c r="J56" s="3"/>
       <c r="K56" s="3"/>
       <c r="L56" s="3"/>
-      <c r="M56" s="36"/>
-      <c r="N56" s="37"/>
+      <c r="M56" s="141"/>
+      <c r="N56" s="142"/>
     </row>
     <row r="57" spans="1:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A57" s="4">
         <v>36</v>
       </c>
-      <c r="B57" s="49" t="s">
+      <c r="B57" s="27" t="s">
         <v>39</v>
       </c>
-      <c r="C57" s="105"/>
-      <c r="D57" s="105"/>
-      <c r="E57" s="105"/>
-      <c r="F57" s="105"/>
-      <c r="G57" s="105"/>
-      <c r="H57" s="105"/>
-      <c r="I57" s="106"/>
+      <c r="C57" s="119"/>
+      <c r="D57" s="119"/>
+      <c r="E57" s="119"/>
+      <c r="F57" s="119"/>
+      <c r="G57" s="119"/>
+      <c r="H57" s="119"/>
+      <c r="I57" s="120"/>
       <c r="J57" s="3"/>
       <c r="K57" s="3"/>
       <c r="L57" s="3"/>
-      <c r="M57" s="36"/>
-      <c r="N57" s="37"/>
+      <c r="M57" s="141"/>
+      <c r="N57" s="142"/>
     </row>
     <row r="58" spans="1:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A58" s="4">
         <v>37</v>
       </c>
-      <c r="B58" s="33" t="s">
+      <c r="B58" s="69" t="s">
         <v>40</v>
       </c>
-      <c r="C58" s="72"/>
-      <c r="D58" s="72"/>
-      <c r="E58" s="72"/>
-      <c r="F58" s="72"/>
-      <c r="G58" s="72"/>
-      <c r="H58" s="72"/>
-      <c r="I58" s="73"/>
+      <c r="C58" s="63"/>
+      <c r="D58" s="63"/>
+      <c r="E58" s="63"/>
+      <c r="F58" s="63"/>
+      <c r="G58" s="63"/>
+      <c r="H58" s="63"/>
+      <c r="I58" s="64"/>
       <c r="J58" s="3"/>
       <c r="K58" s="3"/>
       <c r="L58" s="3"/>
-      <c r="M58" s="36"/>
-      <c r="N58" s="37"/>
+      <c r="M58" s="141"/>
+      <c r="N58" s="142"/>
     </row>
     <row r="59" spans="1:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A59" s="4">
         <v>38</v>
       </c>
-      <c r="B59" s="49" t="s">
+      <c r="B59" s="27" t="s">
         <v>78</v>
       </c>
-      <c r="C59" s="74"/>
-      <c r="D59" s="74"/>
-      <c r="E59" s="74"/>
-      <c r="F59" s="74"/>
-      <c r="G59" s="74"/>
-      <c r="H59" s="74"/>
-      <c r="I59" s="75"/>
+      <c r="C59" s="28"/>
+      <c r="D59" s="28"/>
+      <c r="E59" s="28"/>
+      <c r="F59" s="28"/>
+      <c r="G59" s="28"/>
+      <c r="H59" s="28"/>
+      <c r="I59" s="29"/>
       <c r="J59" s="3"/>
       <c r="K59" s="3"/>
       <c r="L59" s="3"/>
-      <c r="M59" s="36"/>
-      <c r="N59" s="37"/>
+      <c r="M59" s="141"/>
+      <c r="N59" s="142"/>
     </row>
     <row r="60" spans="1:14" ht="21" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A60" s="76" t="s">
+      <c r="A60" s="113" t="s">
         <v>41</v>
       </c>
-      <c r="B60" s="77"/>
-      <c r="C60" s="77"/>
-      <c r="D60" s="77"/>
-      <c r="E60" s="77"/>
-      <c r="F60" s="77"/>
-      <c r="G60" s="77"/>
-      <c r="H60" s="77"/>
-      <c r="I60" s="77"/>
-      <c r="J60" s="77"/>
-      <c r="K60" s="77"/>
-      <c r="L60" s="77"/>
-      <c r="M60" s="77"/>
-      <c r="N60" s="78"/>
+      <c r="B60" s="114"/>
+      <c r="C60" s="114"/>
+      <c r="D60" s="114"/>
+      <c r="E60" s="114"/>
+      <c r="F60" s="114"/>
+      <c r="G60" s="114"/>
+      <c r="H60" s="114"/>
+      <c r="I60" s="114"/>
+      <c r="J60" s="114"/>
+      <c r="K60" s="114"/>
+      <c r="L60" s="114"/>
+      <c r="M60" s="114"/>
+      <c r="N60" s="115"/>
     </row>
     <row r="61" spans="1:14" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A61" s="79"/>
-      <c r="B61" s="80"/>
-      <c r="C61" s="80"/>
-      <c r="D61" s="80"/>
-      <c r="E61" s="80"/>
-      <c r="F61" s="80"/>
-      <c r="G61" s="80"/>
-      <c r="H61" s="80"/>
-      <c r="I61" s="80"/>
-      <c r="J61" s="80"/>
-      <c r="K61" s="80"/>
-      <c r="L61" s="80"/>
-      <c r="M61" s="80"/>
-      <c r="N61" s="81"/>
+      <c r="A61" s="116"/>
+      <c r="B61" s="117"/>
+      <c r="C61" s="117"/>
+      <c r="D61" s="117"/>
+      <c r="E61" s="117"/>
+      <c r="F61" s="117"/>
+      <c r="G61" s="117"/>
+      <c r="H61" s="117"/>
+      <c r="I61" s="117"/>
+      <c r="J61" s="117"/>
+      <c r="K61" s="117"/>
+      <c r="L61" s="117"/>
+      <c r="M61" s="117"/>
+      <c r="N61" s="118"/>
     </row>
     <row r="62" spans="1:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A62" s="57" t="s">
+      <c r="A62" s="104" t="s">
         <v>42</v>
       </c>
-      <c r="B62" s="58"/>
-      <c r="C62" s="58"/>
-      <c r="D62" s="58"/>
-      <c r="E62" s="58"/>
-      <c r="F62" s="58"/>
-      <c r="G62" s="58"/>
-      <c r="H62" s="58"/>
-      <c r="I62" s="58"/>
-      <c r="J62" s="58"/>
-      <c r="K62" s="58"/>
-      <c r="L62" s="58"/>
-      <c r="M62" s="58"/>
-      <c r="N62" s="59"/>
+      <c r="B62" s="105"/>
+      <c r="C62" s="105"/>
+      <c r="D62" s="105"/>
+      <c r="E62" s="105"/>
+      <c r="F62" s="105"/>
+      <c r="G62" s="105"/>
+      <c r="H62" s="105"/>
+      <c r="I62" s="105"/>
+      <c r="J62" s="105"/>
+      <c r="K62" s="105"/>
+      <c r="L62" s="105"/>
+      <c r="M62" s="105"/>
+      <c r="N62" s="106"/>
     </row>
     <row r="63" spans="1:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A63" s="60" t="s">
+      <c r="A63" s="107" t="s">
         <v>43</v>
       </c>
-      <c r="B63" s="61"/>
-      <c r="C63" s="61"/>
-      <c r="D63" s="61"/>
-      <c r="E63" s="61"/>
-      <c r="F63" s="61"/>
-      <c r="G63" s="61"/>
-      <c r="H63" s="61"/>
-      <c r="I63" s="61"/>
-      <c r="J63" s="61"/>
-      <c r="K63" s="61"/>
-      <c r="L63" s="61"/>
-      <c r="M63" s="61"/>
-      <c r="N63" s="62"/>
+      <c r="B63" s="108"/>
+      <c r="C63" s="108"/>
+      <c r="D63" s="108"/>
+      <c r="E63" s="108"/>
+      <c r="F63" s="108"/>
+      <c r="G63" s="108"/>
+      <c r="H63" s="108"/>
+      <c r="I63" s="108"/>
+      <c r="J63" s="108"/>
+      <c r="K63" s="108"/>
+      <c r="L63" s="108"/>
+      <c r="M63" s="108"/>
+      <c r="N63" s="109"/>
     </row>
     <row r="64" spans="1:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A64" s="63" t="s">
+      <c r="A64" s="110" t="s">
         <v>44</v>
       </c>
-      <c r="B64" s="64"/>
-      <c r="C64" s="64"/>
-      <c r="D64" s="64"/>
-      <c r="E64" s="64"/>
-      <c r="F64" s="64"/>
-      <c r="G64" s="64"/>
-      <c r="H64" s="64"/>
-      <c r="I64" s="64"/>
-      <c r="J64" s="64"/>
-      <c r="K64" s="64"/>
-      <c r="L64" s="64"/>
-      <c r="M64" s="64"/>
-      <c r="N64" s="65"/>
+      <c r="B64" s="111"/>
+      <c r="C64" s="111"/>
+      <c r="D64" s="111"/>
+      <c r="E64" s="111"/>
+      <c r="F64" s="111"/>
+      <c r="G64" s="111"/>
+      <c r="H64" s="111"/>
+      <c r="I64" s="111"/>
+      <c r="J64" s="111"/>
+      <c r="K64" s="111"/>
+      <c r="L64" s="111"/>
+      <c r="M64" s="111"/>
+      <c r="N64" s="112"/>
     </row>
     <row r="65" spans="1:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A65" s="63"/>
-      <c r="B65" s="64"/>
-      <c r="C65" s="64"/>
-      <c r="D65" s="64"/>
-      <c r="E65" s="64"/>
-      <c r="F65" s="64"/>
-      <c r="G65" s="64"/>
-      <c r="H65" s="64"/>
-      <c r="I65" s="64"/>
-      <c r="J65" s="64"/>
-      <c r="K65" s="64"/>
-      <c r="L65" s="64"/>
-      <c r="M65" s="64"/>
-      <c r="N65" s="65"/>
+      <c r="A65" s="110"/>
+      <c r="B65" s="111"/>
+      <c r="C65" s="111"/>
+      <c r="D65" s="111"/>
+      <c r="E65" s="111"/>
+      <c r="F65" s="111"/>
+      <c r="G65" s="111"/>
+      <c r="H65" s="111"/>
+      <c r="I65" s="111"/>
+      <c r="J65" s="111"/>
+      <c r="K65" s="111"/>
+      <c r="L65" s="111"/>
+      <c r="M65" s="111"/>
+      <c r="N65" s="112"/>
     </row>
     <row r="66" spans="1:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A66" s="66"/>
-      <c r="B66" s="67"/>
-      <c r="C66" s="67"/>
-      <c r="D66" s="67"/>
-      <c r="E66" s="67"/>
-      <c r="F66" s="67"/>
-      <c r="G66" s="67"/>
-      <c r="H66" s="67"/>
-      <c r="I66" s="67"/>
-      <c r="J66" s="67"/>
-      <c r="K66" s="67"/>
-      <c r="L66" s="67"/>
-      <c r="M66" s="67"/>
-      <c r="N66" s="68"/>
+      <c r="A66" s="98"/>
+      <c r="B66" s="99"/>
+      <c r="C66" s="99"/>
+      <c r="D66" s="99"/>
+      <c r="E66" s="99"/>
+      <c r="F66" s="99"/>
+      <c r="G66" s="99"/>
+      <c r="H66" s="99"/>
+      <c r="I66" s="99"/>
+      <c r="J66" s="99"/>
+      <c r="K66" s="99"/>
+      <c r="L66" s="99"/>
+      <c r="M66" s="99"/>
+      <c r="N66" s="100"/>
     </row>
     <row r="67" spans="1:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A67" s="69"/>
-      <c r="B67" s="70"/>
-      <c r="C67" s="70"/>
-      <c r="D67" s="70"/>
-      <c r="E67" s="70"/>
-      <c r="F67" s="70"/>
-      <c r="G67" s="70"/>
-      <c r="H67" s="70"/>
-      <c r="I67" s="70"/>
-      <c r="J67" s="70"/>
-      <c r="K67" s="70"/>
-      <c r="L67" s="70"/>
-      <c r="M67" s="70"/>
-      <c r="N67" s="71"/>
+      <c r="A67" s="101"/>
+      <c r="B67" s="102"/>
+      <c r="C67" s="102"/>
+      <c r="D67" s="102"/>
+      <c r="E67" s="102"/>
+      <c r="F67" s="102"/>
+      <c r="G67" s="102"/>
+      <c r="H67" s="102"/>
+      <c r="I67" s="102"/>
+      <c r="J67" s="102"/>
+      <c r="K67" s="102"/>
+      <c r="L67" s="102"/>
+      <c r="M67" s="102"/>
+      <c r="N67" s="103"/>
     </row>
     <row r="68" spans="1:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A68" s="66"/>
-      <c r="B68" s="67"/>
-      <c r="C68" s="67"/>
-      <c r="D68" s="67"/>
-      <c r="E68" s="67"/>
-      <c r="F68" s="67"/>
-      <c r="G68" s="67"/>
-      <c r="H68" s="67"/>
-      <c r="I68" s="67"/>
-      <c r="J68" s="67"/>
-      <c r="K68" s="67"/>
-      <c r="L68" s="67"/>
-      <c r="M68" s="67"/>
-      <c r="N68" s="68"/>
+      <c r="A68" s="98"/>
+      <c r="B68" s="99"/>
+      <c r="C68" s="99"/>
+      <c r="D68" s="99"/>
+      <c r="E68" s="99"/>
+      <c r="F68" s="99"/>
+      <c r="G68" s="99"/>
+      <c r="H68" s="99"/>
+      <c r="I68" s="99"/>
+      <c r="J68" s="99"/>
+      <c r="K68" s="99"/>
+      <c r="L68" s="99"/>
+      <c r="M68" s="99"/>
+      <c r="N68" s="100"/>
     </row>
     <row r="69" spans="1:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A69" s="69"/>
-      <c r="B69" s="70"/>
-      <c r="C69" s="70"/>
-      <c r="D69" s="70"/>
-      <c r="E69" s="70"/>
-      <c r="F69" s="70"/>
-      <c r="G69" s="70"/>
-      <c r="H69" s="70"/>
-      <c r="I69" s="70"/>
-      <c r="J69" s="70"/>
-      <c r="K69" s="70"/>
-      <c r="L69" s="70"/>
-      <c r="M69" s="70"/>
-      <c r="N69" s="71"/>
+      <c r="A69" s="101"/>
+      <c r="B69" s="102"/>
+      <c r="C69" s="102"/>
+      <c r="D69" s="102"/>
+      <c r="E69" s="102"/>
+      <c r="F69" s="102"/>
+      <c r="G69" s="102"/>
+      <c r="H69" s="102"/>
+      <c r="I69" s="102"/>
+      <c r="J69" s="102"/>
+      <c r="K69" s="102"/>
+      <c r="L69" s="102"/>
+      <c r="M69" s="102"/>
+      <c r="N69" s="103"/>
     </row>
     <row r="70" spans="1:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A70" s="66"/>
-      <c r="B70" s="67"/>
-      <c r="C70" s="67"/>
-      <c r="D70" s="67"/>
-      <c r="E70" s="67"/>
-      <c r="F70" s="67"/>
-      <c r="G70" s="67"/>
-      <c r="H70" s="67"/>
-      <c r="I70" s="67"/>
-      <c r="J70" s="67"/>
-      <c r="K70" s="67"/>
-      <c r="L70" s="67"/>
-      <c r="M70" s="67"/>
-      <c r="N70" s="68"/>
+      <c r="A70" s="98"/>
+      <c r="B70" s="99"/>
+      <c r="C70" s="99"/>
+      <c r="D70" s="99"/>
+      <c r="E70" s="99"/>
+      <c r="F70" s="99"/>
+      <c r="G70" s="99"/>
+      <c r="H70" s="99"/>
+      <c r="I70" s="99"/>
+      <c r="J70" s="99"/>
+      <c r="K70" s="99"/>
+      <c r="L70" s="99"/>
+      <c r="M70" s="99"/>
+      <c r="N70" s="100"/>
     </row>
     <row r="71" spans="1:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A71" s="69"/>
-      <c r="B71" s="70"/>
-      <c r="C71" s="70"/>
-      <c r="D71" s="70"/>
-      <c r="E71" s="70"/>
-      <c r="F71" s="70"/>
-      <c r="G71" s="70"/>
-      <c r="H71" s="70"/>
-      <c r="I71" s="70"/>
-      <c r="J71" s="70"/>
-      <c r="K71" s="70"/>
-      <c r="L71" s="70"/>
-      <c r="M71" s="70"/>
-      <c r="N71" s="71"/>
+      <c r="A71" s="101"/>
+      <c r="B71" s="102"/>
+      <c r="C71" s="102"/>
+      <c r="D71" s="102"/>
+      <c r="E71" s="102"/>
+      <c r="F71" s="102"/>
+      <c r="G71" s="102"/>
+      <c r="H71" s="102"/>
+      <c r="I71" s="102"/>
+      <c r="J71" s="102"/>
+      <c r="K71" s="102"/>
+      <c r="L71" s="102"/>
+      <c r="M71" s="102"/>
+      <c r="N71" s="103"/>
     </row>
     <row r="72" spans="1:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A72" s="66"/>
-      <c r="B72" s="67"/>
-      <c r="C72" s="67"/>
-      <c r="D72" s="67"/>
-      <c r="E72" s="67"/>
-      <c r="F72" s="67"/>
-      <c r="G72" s="67"/>
-      <c r="H72" s="67"/>
-      <c r="I72" s="67"/>
-      <c r="J72" s="67"/>
-      <c r="K72" s="67"/>
-      <c r="L72" s="67"/>
-      <c r="M72" s="67"/>
-      <c r="N72" s="68"/>
+      <c r="A72" s="98"/>
+      <c r="B72" s="99"/>
+      <c r="C72" s="99"/>
+      <c r="D72" s="99"/>
+      <c r="E72" s="99"/>
+      <c r="F72" s="99"/>
+      <c r="G72" s="99"/>
+      <c r="H72" s="99"/>
+      <c r="I72" s="99"/>
+      <c r="J72" s="99"/>
+      <c r="K72" s="99"/>
+      <c r="L72" s="99"/>
+      <c r="M72" s="99"/>
+      <c r="N72" s="100"/>
     </row>
     <row r="73" spans="1:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A73" s="69"/>
-      <c r="B73" s="70"/>
-      <c r="C73" s="70"/>
-      <c r="D73" s="70"/>
-      <c r="E73" s="70"/>
-      <c r="F73" s="70"/>
-      <c r="G73" s="70"/>
-      <c r="H73" s="70"/>
-      <c r="I73" s="70"/>
-      <c r="J73" s="70"/>
-      <c r="K73" s="70"/>
-      <c r="L73" s="70"/>
-      <c r="M73" s="70"/>
-      <c r="N73" s="71"/>
+      <c r="A73" s="101"/>
+      <c r="B73" s="102"/>
+      <c r="C73" s="102"/>
+      <c r="D73" s="102"/>
+      <c r="E73" s="102"/>
+      <c r="F73" s="102"/>
+      <c r="G73" s="102"/>
+      <c r="H73" s="102"/>
+      <c r="I73" s="102"/>
+      <c r="J73" s="102"/>
+      <c r="K73" s="102"/>
+      <c r="L73" s="102"/>
+      <c r="M73" s="102"/>
+      <c r="N73" s="103"/>
     </row>
     <row r="74" spans="1:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A74" s="66"/>
-      <c r="B74" s="67"/>
-      <c r="C74" s="67"/>
-      <c r="D74" s="67"/>
-      <c r="E74" s="67"/>
-      <c r="F74" s="67"/>
-      <c r="G74" s="67"/>
-      <c r="H74" s="67"/>
-      <c r="I74" s="67"/>
-      <c r="J74" s="67"/>
-      <c r="K74" s="67"/>
-      <c r="L74" s="67"/>
-      <c r="M74" s="67"/>
-      <c r="N74" s="68"/>
+      <c r="A74" s="98"/>
+      <c r="B74" s="99"/>
+      <c r="C74" s="99"/>
+      <c r="D74" s="99"/>
+      <c r="E74" s="99"/>
+      <c r="F74" s="99"/>
+      <c r="G74" s="99"/>
+      <c r="H74" s="99"/>
+      <c r="I74" s="99"/>
+      <c r="J74" s="99"/>
+      <c r="K74" s="99"/>
+      <c r="L74" s="99"/>
+      <c r="M74" s="99"/>
+      <c r="N74" s="100"/>
     </row>
     <row r="75" spans="1:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A75" s="69"/>
-      <c r="B75" s="70"/>
-      <c r="C75" s="70"/>
-      <c r="D75" s="70"/>
-      <c r="E75" s="70"/>
-      <c r="F75" s="70"/>
-      <c r="G75" s="70"/>
-      <c r="H75" s="70"/>
-      <c r="I75" s="70"/>
-      <c r="J75" s="70"/>
-      <c r="K75" s="70"/>
-      <c r="L75" s="70"/>
-      <c r="M75" s="70"/>
-      <c r="N75" s="71"/>
+      <c r="A75" s="101"/>
+      <c r="B75" s="102"/>
+      <c r="C75" s="102"/>
+      <c r="D75" s="102"/>
+      <c r="E75" s="102"/>
+      <c r="F75" s="102"/>
+      <c r="G75" s="102"/>
+      <c r="H75" s="102"/>
+      <c r="I75" s="102"/>
+      <c r="J75" s="102"/>
+      <c r="K75" s="102"/>
+      <c r="L75" s="102"/>
+      <c r="M75" s="102"/>
+      <c r="N75" s="103"/>
     </row>
     <row r="76" spans="1:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A76" s="66"/>
-      <c r="B76" s="67"/>
-      <c r="C76" s="67"/>
-      <c r="D76" s="67"/>
-      <c r="E76" s="67"/>
-      <c r="F76" s="67"/>
-      <c r="G76" s="67"/>
-      <c r="H76" s="67"/>
-      <c r="I76" s="67"/>
-      <c r="J76" s="67"/>
-      <c r="K76" s="67"/>
-      <c r="L76" s="67"/>
-      <c r="M76" s="67"/>
-      <c r="N76" s="68"/>
+      <c r="A76" s="98"/>
+      <c r="B76" s="99"/>
+      <c r="C76" s="99"/>
+      <c r="D76" s="99"/>
+      <c r="E76" s="99"/>
+      <c r="F76" s="99"/>
+      <c r="G76" s="99"/>
+      <c r="H76" s="99"/>
+      <c r="I76" s="99"/>
+      <c r="J76" s="99"/>
+      <c r="K76" s="99"/>
+      <c r="L76" s="99"/>
+      <c r="M76" s="99"/>
+      <c r="N76" s="100"/>
     </row>
     <row r="77" spans="1:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A77" s="69"/>
-      <c r="B77" s="70"/>
-      <c r="C77" s="70"/>
-      <c r="D77" s="70"/>
-      <c r="E77" s="70"/>
-      <c r="F77" s="70"/>
-      <c r="G77" s="70"/>
-      <c r="H77" s="70"/>
-      <c r="I77" s="70"/>
-      <c r="J77" s="70"/>
-      <c r="K77" s="70"/>
-      <c r="L77" s="70"/>
-      <c r="M77" s="70"/>
-      <c r="N77" s="71"/>
+      <c r="A77" s="101"/>
+      <c r="B77" s="102"/>
+      <c r="C77" s="102"/>
+      <c r="D77" s="102"/>
+      <c r="E77" s="102"/>
+      <c r="F77" s="102"/>
+      <c r="G77" s="102"/>
+      <c r="H77" s="102"/>
+      <c r="I77" s="102"/>
+      <c r="J77" s="102"/>
+      <c r="K77" s="102"/>
+      <c r="L77" s="102"/>
+      <c r="M77" s="102"/>
+      <c r="N77" s="103"/>
     </row>
     <row r="78" spans="1:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A78" s="66"/>
-      <c r="B78" s="67"/>
-      <c r="C78" s="67"/>
-      <c r="D78" s="67"/>
-      <c r="E78" s="67"/>
-      <c r="F78" s="67"/>
-      <c r="G78" s="67"/>
-      <c r="H78" s="67"/>
-      <c r="I78" s="67"/>
-      <c r="J78" s="67"/>
-      <c r="K78" s="67"/>
-      <c r="L78" s="67"/>
-      <c r="M78" s="67"/>
-      <c r="N78" s="68"/>
+      <c r="A78" s="98"/>
+      <c r="B78" s="99"/>
+      <c r="C78" s="99"/>
+      <c r="D78" s="99"/>
+      <c r="E78" s="99"/>
+      <c r="F78" s="99"/>
+      <c r="G78" s="99"/>
+      <c r="H78" s="99"/>
+      <c r="I78" s="99"/>
+      <c r="J78" s="99"/>
+      <c r="K78" s="99"/>
+      <c r="L78" s="99"/>
+      <c r="M78" s="99"/>
+      <c r="N78" s="100"/>
     </row>
     <row r="79" spans="1:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A79" s="69"/>
-      <c r="B79" s="70"/>
-      <c r="C79" s="70"/>
-      <c r="D79" s="70"/>
-      <c r="E79" s="70"/>
-      <c r="F79" s="70"/>
-      <c r="G79" s="70"/>
-      <c r="H79" s="70"/>
-      <c r="I79" s="70"/>
-      <c r="J79" s="70"/>
-      <c r="K79" s="70"/>
-      <c r="L79" s="70"/>
-      <c r="M79" s="70"/>
-      <c r="N79" s="71"/>
+      <c r="A79" s="101"/>
+      <c r="B79" s="102"/>
+      <c r="C79" s="102"/>
+      <c r="D79" s="102"/>
+      <c r="E79" s="102"/>
+      <c r="F79" s="102"/>
+      <c r="G79" s="102"/>
+      <c r="H79" s="102"/>
+      <c r="I79" s="102"/>
+      <c r="J79" s="102"/>
+      <c r="K79" s="102"/>
+      <c r="L79" s="102"/>
+      <c r="M79" s="102"/>
+      <c r="N79" s="103"/>
     </row>
     <row r="80" spans="1:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A80" s="66"/>
-      <c r="B80" s="67"/>
-      <c r="C80" s="67"/>
-      <c r="D80" s="67"/>
-      <c r="E80" s="67"/>
-      <c r="F80" s="67"/>
-      <c r="G80" s="67"/>
-      <c r="H80" s="67"/>
-      <c r="I80" s="67"/>
-      <c r="J80" s="67"/>
-      <c r="K80" s="67"/>
-      <c r="L80" s="67"/>
-      <c r="M80" s="67"/>
-      <c r="N80" s="68"/>
+      <c r="A80" s="98"/>
+      <c r="B80" s="99"/>
+      <c r="C80" s="99"/>
+      <c r="D80" s="99"/>
+      <c r="E80" s="99"/>
+      <c r="F80" s="99"/>
+      <c r="G80" s="99"/>
+      <c r="H80" s="99"/>
+      <c r="I80" s="99"/>
+      <c r="J80" s="99"/>
+      <c r="K80" s="99"/>
+      <c r="L80" s="99"/>
+      <c r="M80" s="99"/>
+      <c r="N80" s="100"/>
     </row>
     <row r="81" spans="1:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A81" s="69"/>
-      <c r="B81" s="70"/>
-      <c r="C81" s="70"/>
-      <c r="D81" s="70"/>
-      <c r="E81" s="70"/>
-      <c r="F81" s="70"/>
-      <c r="G81" s="70"/>
-      <c r="H81" s="70"/>
-      <c r="I81" s="70"/>
-      <c r="J81" s="70"/>
-      <c r="K81" s="70"/>
-      <c r="L81" s="70"/>
-      <c r="M81" s="70"/>
-      <c r="N81" s="71"/>
+      <c r="A81" s="101"/>
+      <c r="B81" s="102"/>
+      <c r="C81" s="102"/>
+      <c r="D81" s="102"/>
+      <c r="E81" s="102"/>
+      <c r="F81" s="102"/>
+      <c r="G81" s="102"/>
+      <c r="H81" s="102"/>
+      <c r="I81" s="102"/>
+      <c r="J81" s="102"/>
+      <c r="K81" s="102"/>
+      <c r="L81" s="102"/>
+      <c r="M81" s="102"/>
+      <c r="N81" s="103"/>
     </row>
     <row r="82" spans="1:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A82" s="66"/>
-      <c r="B82" s="67"/>
-      <c r="C82" s="67"/>
-      <c r="D82" s="67"/>
-      <c r="E82" s="67"/>
-      <c r="F82" s="67"/>
-      <c r="G82" s="67"/>
-      <c r="H82" s="67"/>
-      <c r="I82" s="67"/>
-      <c r="J82" s="67"/>
-      <c r="K82" s="67"/>
-      <c r="L82" s="67"/>
-      <c r="M82" s="67"/>
-      <c r="N82" s="68"/>
+      <c r="A82" s="98"/>
+      <c r="B82" s="99"/>
+      <c r="C82" s="99"/>
+      <c r="D82" s="99"/>
+      <c r="E82" s="99"/>
+      <c r="F82" s="99"/>
+      <c r="G82" s="99"/>
+      <c r="H82" s="99"/>
+      <c r="I82" s="99"/>
+      <c r="J82" s="99"/>
+      <c r="K82" s="99"/>
+      <c r="L82" s="99"/>
+      <c r="M82" s="99"/>
+      <c r="N82" s="100"/>
     </row>
     <row r="83" spans="1:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A83" s="69"/>
-      <c r="B83" s="70"/>
-      <c r="C83" s="70"/>
-      <c r="D83" s="70"/>
-      <c r="E83" s="70"/>
-      <c r="F83" s="70"/>
-      <c r="G83" s="70"/>
-      <c r="H83" s="70"/>
-      <c r="I83" s="70"/>
-      <c r="J83" s="70"/>
-      <c r="K83" s="70"/>
-      <c r="L83" s="70"/>
-      <c r="M83" s="70"/>
-      <c r="N83" s="71"/>
+      <c r="A83" s="101"/>
+      <c r="B83" s="102"/>
+      <c r="C83" s="102"/>
+      <c r="D83" s="102"/>
+      <c r="E83" s="102"/>
+      <c r="F83" s="102"/>
+      <c r="G83" s="102"/>
+      <c r="H83" s="102"/>
+      <c r="I83" s="102"/>
+      <c r="J83" s="102"/>
+      <c r="K83" s="102"/>
+      <c r="L83" s="102"/>
+      <c r="M83" s="102"/>
+      <c r="N83" s="103"/>
     </row>
     <row r="84" spans="1:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A84" s="13"/>
@@ -6413,75 +6450,184 @@
       <c r="N89" s="6"/>
     </row>
     <row r="90" spans="1:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A90" s="82" t="s">
+      <c r="A90" s="75" t="s">
         <v>46</v>
       </c>
-      <c r="B90" s="83"/>
-      <c r="C90" s="83"/>
-      <c r="D90" s="83"/>
-      <c r="E90" s="83"/>
-      <c r="F90" s="84"/>
+      <c r="B90" s="76"/>
+      <c r="C90" s="76"/>
+      <c r="D90" s="76"/>
+      <c r="E90" s="76"/>
+      <c r="F90" s="77"/>
       <c r="G90" s="17" t="s">
         <v>47</v>
       </c>
       <c r="H90" s="17" t="s">
         <v>48</v>
       </c>
-      <c r="I90" s="82" t="s">
+      <c r="I90" s="75" t="s">
         <v>49</v>
       </c>
-      <c r="J90" s="83"/>
-      <c r="K90" s="84"/>
-      <c r="L90" s="82" t="s">
+      <c r="J90" s="76"/>
+      <c r="K90" s="77"/>
+      <c r="L90" s="75" t="s">
         <v>50</v>
       </c>
-      <c r="M90" s="83"/>
-      <c r="N90" s="84"/>
+      <c r="M90" s="76"/>
+      <c r="N90" s="77"/>
     </row>
     <row r="91" spans="1:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A91" s="85" t="s">
+      <c r="A91" s="78" t="s">
         <v>69</v>
       </c>
-      <c r="B91" s="86"/>
-      <c r="C91" s="86"/>
-      <c r="D91" s="86"/>
-      <c r="E91" s="86"/>
-      <c r="F91" s="87"/>
-      <c r="G91" s="91" t="s">
+      <c r="B91" s="79"/>
+      <c r="C91" s="79"/>
+      <c r="D91" s="79"/>
+      <c r="E91" s="79"/>
+      <c r="F91" s="80"/>
+      <c r="G91" s="84" t="s">
         <v>70</v>
       </c>
-      <c r="H91" s="87" t="s">
+      <c r="H91" s="80" t="s">
         <v>71</v>
       </c>
-      <c r="I91" s="93">
+      <c r="I91" s="86">
         <v>45840</v>
       </c>
-      <c r="J91" s="94"/>
-      <c r="K91" s="95"/>
-      <c r="L91" s="99" t="s">
+      <c r="J91" s="87"/>
+      <c r="K91" s="88"/>
+      <c r="L91" s="92" t="s">
         <v>51</v>
       </c>
-      <c r="M91" s="100"/>
-      <c r="N91" s="101"/>
+      <c r="M91" s="93"/>
+      <c r="N91" s="94"/>
     </row>
     <row r="92" spans="1:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A92" s="88"/>
-      <c r="B92" s="89"/>
-      <c r="C92" s="89"/>
-      <c r="D92" s="89"/>
-      <c r="E92" s="89"/>
-      <c r="F92" s="90"/>
-      <c r="G92" s="92"/>
-      <c r="H92" s="90"/>
-      <c r="I92" s="96"/>
-      <c r="J92" s="97"/>
-      <c r="K92" s="98"/>
-      <c r="L92" s="102"/>
-      <c r="M92" s="103"/>
-      <c r="N92" s="104"/>
+      <c r="A92" s="81"/>
+      <c r="B92" s="82"/>
+      <c r="C92" s="82"/>
+      <c r="D92" s="82"/>
+      <c r="E92" s="82"/>
+      <c r="F92" s="83"/>
+      <c r="G92" s="85"/>
+      <c r="H92" s="83"/>
+      <c r="I92" s="89"/>
+      <c r="J92" s="90"/>
+      <c r="K92" s="91"/>
+      <c r="L92" s="95"/>
+      <c r="M92" s="96"/>
+      <c r="N92" s="97"/>
     </row>
   </sheetData>
   <mergeCells count="133">
+    <mergeCell ref="I9:N9"/>
+    <mergeCell ref="E9:H9"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="D1:L3"/>
+    <mergeCell ref="M1:N3"/>
+    <mergeCell ref="B36:I36"/>
+    <mergeCell ref="M36:N36"/>
+    <mergeCell ref="B28:I28"/>
+    <mergeCell ref="B29:I29"/>
+    <mergeCell ref="M28:N28"/>
+    <mergeCell ref="M29:N29"/>
+    <mergeCell ref="M30:N30"/>
+    <mergeCell ref="B30:I30"/>
+    <mergeCell ref="A31:N31"/>
+    <mergeCell ref="B32:I32"/>
+    <mergeCell ref="M32:N32"/>
+    <mergeCell ref="A34:N34"/>
+    <mergeCell ref="B33:I33"/>
+    <mergeCell ref="M33:N33"/>
+    <mergeCell ref="B35:I35"/>
+    <mergeCell ref="M35:N35"/>
+    <mergeCell ref="B27:I27"/>
+    <mergeCell ref="M27:N27"/>
+    <mergeCell ref="B25:I25"/>
+    <mergeCell ref="M25:N25"/>
+    <mergeCell ref="B26:I26"/>
+    <mergeCell ref="M26:N26"/>
+    <mergeCell ref="A62:N62"/>
+    <mergeCell ref="A63:N63"/>
+    <mergeCell ref="A64:N65"/>
+    <mergeCell ref="A66:N67"/>
+    <mergeCell ref="A68:N69"/>
+    <mergeCell ref="A70:N71"/>
+    <mergeCell ref="B58:I58"/>
+    <mergeCell ref="M58:N58"/>
+    <mergeCell ref="B59:I59"/>
+    <mergeCell ref="M59:N59"/>
+    <mergeCell ref="A60:N60"/>
+    <mergeCell ref="A61:N61"/>
+    <mergeCell ref="B55:I55"/>
+    <mergeCell ref="M55:N55"/>
+    <mergeCell ref="B56:I56"/>
+    <mergeCell ref="M56:N56"/>
+    <mergeCell ref="B57:I57"/>
+    <mergeCell ref="M57:N57"/>
+    <mergeCell ref="A50:N50"/>
+    <mergeCell ref="B51:I51"/>
+    <mergeCell ref="B52:I52"/>
+    <mergeCell ref="A90:F90"/>
+    <mergeCell ref="I90:K90"/>
+    <mergeCell ref="L90:N90"/>
+    <mergeCell ref="A91:F92"/>
+    <mergeCell ref="G91:G92"/>
+    <mergeCell ref="H91:H92"/>
+    <mergeCell ref="I91:K92"/>
+    <mergeCell ref="L91:N92"/>
+    <mergeCell ref="A72:N73"/>
+    <mergeCell ref="A74:N75"/>
+    <mergeCell ref="A76:N77"/>
+    <mergeCell ref="A78:N79"/>
+    <mergeCell ref="A80:N81"/>
+    <mergeCell ref="A82:N83"/>
+    <mergeCell ref="A54:N54"/>
+    <mergeCell ref="B37:I37"/>
+    <mergeCell ref="M37:N37"/>
+    <mergeCell ref="B38:I38"/>
+    <mergeCell ref="M38:N38"/>
+    <mergeCell ref="A46:N46"/>
+    <mergeCell ref="B47:I47"/>
+    <mergeCell ref="M47:N47"/>
+    <mergeCell ref="A39:N39"/>
+    <mergeCell ref="B40:I40"/>
+    <mergeCell ref="B41:I41"/>
+    <mergeCell ref="M52:N52"/>
+    <mergeCell ref="B53:I53"/>
+    <mergeCell ref="M53:N53"/>
+    <mergeCell ref="M51:N51"/>
+    <mergeCell ref="B48:I48"/>
+    <mergeCell ref="M48:N48"/>
+    <mergeCell ref="B49:I49"/>
+    <mergeCell ref="M49:N49"/>
+    <mergeCell ref="B42:I42"/>
+    <mergeCell ref="B43:I43"/>
+    <mergeCell ref="B45:I45"/>
+    <mergeCell ref="M45:N45"/>
+    <mergeCell ref="B21:I21"/>
+    <mergeCell ref="M21:N21"/>
+    <mergeCell ref="A23:N23"/>
+    <mergeCell ref="B24:I24"/>
+    <mergeCell ref="M24:N24"/>
+    <mergeCell ref="B18:I18"/>
+    <mergeCell ref="M18:N18"/>
+    <mergeCell ref="B19:I19"/>
+    <mergeCell ref="M19:N19"/>
+    <mergeCell ref="B20:I20"/>
+    <mergeCell ref="M20:N20"/>
+    <mergeCell ref="B22:I22"/>
+    <mergeCell ref="M22:N22"/>
+    <mergeCell ref="B15:I15"/>
+    <mergeCell ref="M15:N15"/>
+    <mergeCell ref="B16:I16"/>
+    <mergeCell ref="M16:N16"/>
+    <mergeCell ref="B17:I17"/>
+    <mergeCell ref="M17:N17"/>
+    <mergeCell ref="I12:N12"/>
+    <mergeCell ref="A13:I13"/>
+    <mergeCell ref="M13:N13"/>
+    <mergeCell ref="A14:N14"/>
+    <mergeCell ref="A12:G12"/>
     <mergeCell ref="A8:D8"/>
     <mergeCell ref="E8:H8"/>
     <mergeCell ref="I8:N8"/>
@@ -6506,116 +6652,15 @@
     <mergeCell ref="E5:H5"/>
     <mergeCell ref="I5:N5"/>
     <mergeCell ref="A11:N11"/>
-    <mergeCell ref="B15:I15"/>
-    <mergeCell ref="M15:N15"/>
-    <mergeCell ref="B16:I16"/>
-    <mergeCell ref="M16:N16"/>
-    <mergeCell ref="B17:I17"/>
-    <mergeCell ref="M17:N17"/>
-    <mergeCell ref="I12:N12"/>
-    <mergeCell ref="A13:I13"/>
-    <mergeCell ref="M13:N13"/>
-    <mergeCell ref="A14:N14"/>
-    <mergeCell ref="A12:G12"/>
-    <mergeCell ref="B21:I21"/>
-    <mergeCell ref="M21:N21"/>
-    <mergeCell ref="A23:N23"/>
-    <mergeCell ref="B24:I24"/>
-    <mergeCell ref="M24:N24"/>
-    <mergeCell ref="B18:I18"/>
-    <mergeCell ref="M18:N18"/>
-    <mergeCell ref="B19:I19"/>
-    <mergeCell ref="M19:N19"/>
-    <mergeCell ref="B20:I20"/>
-    <mergeCell ref="M20:N20"/>
-    <mergeCell ref="B22:I22"/>
-    <mergeCell ref="M22:N22"/>
-    <mergeCell ref="A54:N54"/>
-    <mergeCell ref="B37:I37"/>
-    <mergeCell ref="M37:N37"/>
-    <mergeCell ref="B38:I38"/>
-    <mergeCell ref="M38:N38"/>
-    <mergeCell ref="A46:N46"/>
-    <mergeCell ref="B47:I47"/>
-    <mergeCell ref="M47:N47"/>
-    <mergeCell ref="A39:N39"/>
-    <mergeCell ref="B40:I40"/>
-    <mergeCell ref="B41:I41"/>
-    <mergeCell ref="M52:N52"/>
-    <mergeCell ref="B53:I53"/>
-    <mergeCell ref="M53:N53"/>
-    <mergeCell ref="M51:N51"/>
-    <mergeCell ref="B48:I48"/>
-    <mergeCell ref="M48:N48"/>
-    <mergeCell ref="B49:I49"/>
-    <mergeCell ref="M49:N49"/>
-    <mergeCell ref="B42:I42"/>
-    <mergeCell ref="B43:I43"/>
-    <mergeCell ref="B45:I45"/>
-    <mergeCell ref="M45:N45"/>
-    <mergeCell ref="A90:F90"/>
-    <mergeCell ref="I90:K90"/>
-    <mergeCell ref="L90:N90"/>
-    <mergeCell ref="A91:F92"/>
-    <mergeCell ref="G91:G92"/>
-    <mergeCell ref="H91:H92"/>
-    <mergeCell ref="I91:K92"/>
-    <mergeCell ref="L91:N92"/>
-    <mergeCell ref="A72:N73"/>
-    <mergeCell ref="A74:N75"/>
-    <mergeCell ref="A76:N77"/>
-    <mergeCell ref="A78:N79"/>
-    <mergeCell ref="A80:N81"/>
-    <mergeCell ref="A82:N83"/>
-    <mergeCell ref="M25:N25"/>
-    <mergeCell ref="B26:I26"/>
-    <mergeCell ref="M26:N26"/>
-    <mergeCell ref="A62:N62"/>
-    <mergeCell ref="A63:N63"/>
-    <mergeCell ref="A64:N65"/>
-    <mergeCell ref="A66:N67"/>
-    <mergeCell ref="A68:N69"/>
-    <mergeCell ref="A70:N71"/>
-    <mergeCell ref="B58:I58"/>
-    <mergeCell ref="M58:N58"/>
-    <mergeCell ref="B59:I59"/>
-    <mergeCell ref="M59:N59"/>
-    <mergeCell ref="A60:N60"/>
-    <mergeCell ref="A61:N61"/>
-    <mergeCell ref="B55:I55"/>
-    <mergeCell ref="M55:N55"/>
-    <mergeCell ref="B56:I56"/>
-    <mergeCell ref="M56:N56"/>
-    <mergeCell ref="B57:I57"/>
-    <mergeCell ref="M57:N57"/>
-    <mergeCell ref="A50:N50"/>
-    <mergeCell ref="B51:I51"/>
-    <mergeCell ref="B52:I52"/>
-    <mergeCell ref="I9:N9"/>
-    <mergeCell ref="E9:H9"/>
-    <mergeCell ref="A9:D9"/>
-    <mergeCell ref="D1:L3"/>
-    <mergeCell ref="M1:N3"/>
-    <mergeCell ref="B36:I36"/>
-    <mergeCell ref="M36:N36"/>
-    <mergeCell ref="B28:I28"/>
-    <mergeCell ref="B29:I29"/>
-    <mergeCell ref="M28:N28"/>
-    <mergeCell ref="M29:N29"/>
-    <mergeCell ref="M30:N30"/>
-    <mergeCell ref="B30:I30"/>
-    <mergeCell ref="A31:N31"/>
-    <mergeCell ref="B32:I32"/>
-    <mergeCell ref="M32:N32"/>
-    <mergeCell ref="A34:N34"/>
-    <mergeCell ref="B33:I33"/>
-    <mergeCell ref="M33:N33"/>
-    <mergeCell ref="B35:I35"/>
-    <mergeCell ref="M35:N35"/>
-    <mergeCell ref="B27:I27"/>
-    <mergeCell ref="M27:N27"/>
-    <mergeCell ref="B25:I25"/>
   </mergeCells>
+  <conditionalFormatting sqref="J1:L1048576">
+    <cfRule type="containsText" dxfId="1" priority="1" operator="containsText" text="FALHA">
+      <formula>NOT(ISERROR(SEARCH("FALHA",J1)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="0" priority="2" operator="containsText" text="ok">
+      <formula>NOT(ISERROR(SEARCH("ok",J1)))</formula>
+    </cfRule>
+  </conditionalFormatting>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0.19685039370078741" right="0.19685039370078741" top="0.19685039370078741" bottom="0.19685039370078741" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup paperSize="9" scale="56" fitToHeight="2" orientation="portrait" r:id="rId1"/>
@@ -6627,26 +6672,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="7b8015c9-aad1-4bac-8950-78e0ae91757b">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="05331b14-7a17-452c-bd43-8b05eb5f4a9a" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x01010005D774826369C743B955A0E424486114" ma:contentTypeVersion="10" ma:contentTypeDescription="Crie um novo documento." ma:contentTypeScope="" ma:versionID="b356397a8ff3f0f3ef347bf56839840a">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="7b8015c9-aad1-4bac-8950-78e0ae91757b" xmlns:ns3="05331b14-7a17-452c-bd43-8b05eb5f4a9a" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="5b083322ca4a580c85923f4f89f565b7" ns2:_="" ns3:_="">
     <xsd:import namespace="7b8015c9-aad1-4bac-8950-78e0ae91757b"/>
@@ -6835,26 +6860,27 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CB2889E8-3056-4614-BA74-B4FA4C061B0A}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="7b8015c9-aad1-4bac-8950-78e0ae91757b"/>
-    <ds:schemaRef ds:uri="05331b14-7a17-452c-bd43-8b05eb5f4a9a"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B7B19BC3-2D21-41B0-ACB2-31D21A31FA78}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="7b8015c9-aad1-4bac-8950-78e0ae91757b">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="05331b14-7a17-452c-bd43-8b05eb5f4a9a" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{01C64FFA-C8B1-4566-BF60-B745BBB94341}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -6871,4 +6897,23 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B7B19BC3-2D21-41B0-ACB2-31D21A31FA78}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CB2889E8-3056-4614-BA74-B4FA4C061B0A}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="7b8015c9-aad1-4bac-8950-78e0ae91757b"/>
+    <ds:schemaRef ds:uri="05331b14-7a17-452c-bd43-8b05eb5f4a9a"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>